--- a/DMA350_Testlist_Report.xlsx
+++ b/DMA350_Testlist_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83377f57b735e897/Máy tính/DMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2625DCD3-86CB-454F-AA68-A012DEAA1CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{2625DCD3-86CB-454F-AA68-A012DEAA1CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E45DFA8-0294-46C0-B692-ECDF5AA7947D}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5EF85DA-40B8-41A9-8419-62FC068EFE4F}"/>
   </bookViews>
@@ -1146,22 +1146,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1198,14 +1186,29 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1543,10 +1546,10 @@
   <dimension ref="A1:AQ53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.77734375" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" customWidth="1"/>
-    <col min="4" max="4" width="42.77734375" customWidth="1"/>
+    <col min="1" max="1" width="5.77734375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="33" style="1" customWidth="1"/>
     <col min="5" max="5" width="52.77734375" customWidth="1"/>
     <col min="6" max="6" width="40.77734375" customWidth="1"/>
     <col min="7" max="7" width="60.77734375" customWidth="1"/>
@@ -1555,3869 +1558,3870 @@
     <col min="10" max="11" width="12.77734375" customWidth="1"/>
     <col min="12" max="13" width="13.77734375" customWidth="1"/>
     <col min="14" max="14" width="18.77734375" customWidth="1"/>
+    <col min="17" max="17" width="29" customWidth="1"/>
     <col min="41" max="41" width="30.77734375" customWidth="1"/>
     <col min="42" max="42" width="12.77734375" customWidth="1"/>
     <col min="43" max="43" width="40.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-      <c r="AB1" s="3"/>
-      <c r="AC1" s="3"/>
-      <c r="AD1" s="3"/>
-      <c r="AE1" s="3"/>
-      <c r="AF1" s="3"/>
-      <c r="AG1" s="3"/>
-      <c r="AH1" s="3"/>
-      <c r="AI1" s="3"/>
-      <c r="AJ1" s="3"/>
-      <c r="AK1" s="3"/>
-      <c r="AL1" s="3"/>
-      <c r="AM1" s="3"/>
-      <c r="AN1" s="3"/>
-      <c r="AO1" s="3"/>
-      <c r="AP1" s="3"/>
-      <c r="AQ1" s="3"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="21"/>
+      <c r="U1" s="21"/>
+      <c r="V1" s="21"/>
+      <c r="W1" s="21"/>
+      <c r="X1" s="21"/>
+      <c r="Y1" s="21"/>
+      <c r="Z1" s="21"/>
+      <c r="AA1" s="21"/>
+      <c r="AB1" s="21"/>
+      <c r="AC1" s="21"/>
+      <c r="AD1" s="21"/>
+      <c r="AE1" s="21"/>
+      <c r="AF1" s="21"/>
+      <c r="AG1" s="21"/>
+      <c r="AH1" s="21"/>
+      <c r="AI1" s="21"/>
+      <c r="AJ1" s="21"/>
+      <c r="AK1" s="21"/>
+      <c r="AL1" s="21"/>
+      <c r="AM1" s="21"/>
+      <c r="AN1" s="21"/>
+      <c r="AO1" s="21"/>
+      <c r="AP1" s="21"/>
+      <c r="AQ1" s="21"/>
     </row>
     <row r="2" spans="1:43" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
-      <c r="AF2" s="5"/>
-      <c r="AG2" s="5"/>
-      <c r="AH2" s="5"/>
-      <c r="AI2" s="5"/>
-      <c r="AJ2" s="5"/>
-      <c r="AK2" s="5"/>
-      <c r="AL2" s="5"/>
-      <c r="AM2" s="5"/>
-      <c r="AN2" s="5"/>
-      <c r="AO2" s="5"/>
-      <c r="AP2" s="5"/>
-      <c r="AQ2" s="5"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="23"/>
+      <c r="W2" s="23"/>
+      <c r="X2" s="23"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="23"/>
+      <c r="AA2" s="23"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="23"/>
+      <c r="AD2" s="23"/>
+      <c r="AE2" s="23"/>
+      <c r="AF2" s="23"/>
+      <c r="AG2" s="23"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="23"/>
+      <c r="AJ2" s="23"/>
+      <c r="AK2" s="23"/>
+      <c r="AL2" s="23"/>
+      <c r="AM2" s="23"/>
+      <c r="AN2" s="23"/>
+      <c r="AO2" s="23"/>
+      <c r="AP2" s="23"/>
+      <c r="AQ2" s="23"/>
     </row>
     <row r="3" spans="1:43" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="L3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="8" t="s">
+      <c r="N3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="P3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="Q3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="8"/>
-      <c r="U3" s="8"/>
-      <c r="V3" s="8"/>
-      <c r="W3" s="8"/>
-      <c r="X3" s="8"/>
-      <c r="Y3" s="8"/>
-      <c r="Z3" s="8"/>
-      <c r="AA3" s="8"/>
-      <c r="AB3" s="8"/>
-      <c r="AC3" s="8"/>
-      <c r="AD3" s="8"/>
-      <c r="AE3" s="8"/>
-      <c r="AF3" s="8"/>
-      <c r="AG3" s="8"/>
-      <c r="AH3" s="8"/>
-      <c r="AI3" s="8"/>
-      <c r="AJ3" s="8"/>
-      <c r="AK3" s="8"/>
-      <c r="AL3" s="8"/>
-      <c r="AM3" s="8"/>
-      <c r="AN3" s="8"/>
-      <c r="AO3" s="8"/>
-      <c r="AP3" s="8"/>
-      <c r="AQ3" s="8"/>
+      <c r="R3" s="4"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="4"/>
+      <c r="W3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="4"/>
+      <c r="AB3" s="4"/>
+      <c r="AC3" s="4"/>
+      <c r="AD3" s="4"/>
+      <c r="AE3" s="4"/>
+      <c r="AF3" s="4"/>
+      <c r="AG3" s="4"/>
+      <c r="AH3" s="4"/>
+      <c r="AI3" s="4"/>
+      <c r="AJ3" s="4"/>
+      <c r="AK3" s="4"/>
+      <c r="AL3" s="4"/>
+      <c r="AM3" s="4"/>
+      <c r="AN3" s="4"/>
+      <c r="AO3" s="4"/>
+      <c r="AP3" s="4"/>
+      <c r="AQ3" s="4"/>
     </row>
     <row r="4" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
+      <c r="A4" s="5">
         <v>1</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="J4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="K4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M4" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N4" s="10" t="s">
+      <c r="L4" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M4" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="10" t="s">
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="10"/>
-      <c r="X4" s="10"/>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-      <c r="AB4" s="10"/>
-      <c r="AC4" s="10"/>
-      <c r="AD4" s="10"/>
-      <c r="AE4" s="10"/>
-      <c r="AF4" s="10"/>
-      <c r="AG4" s="10"/>
-      <c r="AH4" s="10"/>
-      <c r="AI4" s="10"/>
-      <c r="AJ4" s="10"/>
-      <c r="AK4" s="10"/>
-      <c r="AL4" s="10"/>
-      <c r="AM4" s="10"/>
-      <c r="AN4" s="10"/>
-      <c r="AO4" s="10"/>
-      <c r="AP4" s="10"/>
-      <c r="AQ4" s="10"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="6"/>
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="6"/>
+      <c r="AF4" s="6"/>
+      <c r="AG4" s="6"/>
+      <c r="AH4" s="6"/>
+      <c r="AI4" s="6"/>
+      <c r="AJ4" s="6"/>
+      <c r="AK4" s="6"/>
+      <c r="AL4" s="6"/>
+      <c r="AM4" s="6"/>
+      <c r="AN4" s="6"/>
+      <c r="AO4" s="6"/>
+      <c r="AP4" s="6"/>
+      <c r="AQ4" s="6"/>
     </row>
     <row r="5" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
+      <c r="A5" s="8">
         <v>2</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="J5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L5" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M5" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N5" s="13" t="s">
+      <c r="L5" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M5" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N5" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="13"/>
-      <c r="V5" s="13"/>
-      <c r="W5" s="13"/>
-      <c r="X5" s="13"/>
-      <c r="Y5" s="13"/>
-      <c r="Z5" s="13"/>
-      <c r="AA5" s="13"/>
-      <c r="AB5" s="13"/>
-      <c r="AC5" s="13"/>
-      <c r="AD5" s="13"/>
-      <c r="AE5" s="13"/>
-      <c r="AF5" s="13"/>
-      <c r="AG5" s="13"/>
-      <c r="AH5" s="13"/>
-      <c r="AI5" s="13"/>
-      <c r="AJ5" s="13"/>
-      <c r="AK5" s="13"/>
-      <c r="AL5" s="13"/>
-      <c r="AM5" s="13"/>
-      <c r="AN5" s="13"/>
-      <c r="AO5" s="13"/>
-      <c r="AP5" s="13"/>
-      <c r="AQ5" s="13"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="9"/>
+      <c r="AB5" s="9"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="9"/>
+      <c r="AF5" s="9"/>
+      <c r="AG5" s="9"/>
+      <c r="AH5" s="9"/>
+      <c r="AI5" s="9"/>
+      <c r="AJ5" s="9"/>
+      <c r="AK5" s="9"/>
+      <c r="AL5" s="9"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="9"/>
+      <c r="AP5" s="9"/>
+      <c r="AQ5" s="9"/>
     </row>
     <row r="6" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
+      <c r="A6" s="5">
         <v>3</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="J6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M6" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N6" s="10" t="s">
+      <c r="L6" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M6" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
-      <c r="W6" s="10"/>
-      <c r="X6" s="10"/>
-      <c r="Y6" s="10"/>
-      <c r="Z6" s="10"/>
-      <c r="AA6" s="10"/>
-      <c r="AB6" s="10"/>
-      <c r="AC6" s="10"/>
-      <c r="AD6" s="10"/>
-      <c r="AE6" s="10"/>
-      <c r="AF6" s="10"/>
-      <c r="AG6" s="10"/>
-      <c r="AH6" s="10"/>
-      <c r="AI6" s="10"/>
-      <c r="AJ6" s="10"/>
-      <c r="AK6" s="10"/>
-      <c r="AL6" s="10"/>
-      <c r="AM6" s="10"/>
-      <c r="AN6" s="10"/>
-      <c r="AO6" s="10"/>
-      <c r="AP6" s="10"/>
-      <c r="AQ6" s="10"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="6"/>
+      <c r="AA6" s="6"/>
+      <c r="AB6" s="6"/>
+      <c r="AC6" s="6"/>
+      <c r="AD6" s="6"/>
+      <c r="AE6" s="6"/>
+      <c r="AF6" s="6"/>
+      <c r="AG6" s="6"/>
+      <c r="AH6" s="6"/>
+      <c r="AI6" s="6"/>
+      <c r="AJ6" s="6"/>
+      <c r="AK6" s="6"/>
+      <c r="AL6" s="6"/>
+      <c r="AM6" s="6"/>
+      <c r="AN6" s="6"/>
+      <c r="AO6" s="6"/>
+      <c r="AP6" s="6"/>
+      <c r="AQ6" s="6"/>
     </row>
     <row r="7" spans="1:43" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+      <c r="A7" s="8">
         <v>4</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="16" t="s">
+      <c r="J7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L7" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M7" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N7" s="13" t="s">
+      <c r="L7" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M7" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N7" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13" t="s">
+      <c r="O7" s="9"/>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="13"/>
-      <c r="V7" s="13"/>
-      <c r="W7" s="13"/>
-      <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="13"/>
-      <c r="AA7" s="13"/>
-      <c r="AB7" s="13"/>
-      <c r="AC7" s="13"/>
-      <c r="AD7" s="13"/>
-      <c r="AE7" s="13"/>
-      <c r="AF7" s="13"/>
-      <c r="AG7" s="13"/>
-      <c r="AH7" s="13"/>
-      <c r="AI7" s="13"/>
-      <c r="AJ7" s="13"/>
-      <c r="AK7" s="13"/>
-      <c r="AL7" s="13"/>
-      <c r="AM7" s="13"/>
-      <c r="AN7" s="13"/>
-      <c r="AO7" s="13"/>
-      <c r="AP7" s="13"/>
-      <c r="AQ7" s="13"/>
+      <c r="R7" s="9"/>
+      <c r="S7" s="9"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="9"/>
+      <c r="V7" s="9"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+      <c r="Z7" s="9"/>
+      <c r="AA7" s="9"/>
+      <c r="AB7" s="9"/>
+      <c r="AC7" s="9"/>
+      <c r="AD7" s="9"/>
+      <c r="AE7" s="9"/>
+      <c r="AF7" s="9"/>
+      <c r="AG7" s="9"/>
+      <c r="AH7" s="9"/>
+      <c r="AI7" s="9"/>
+      <c r="AJ7" s="9"/>
+      <c r="AK7" s="9"/>
+      <c r="AL7" s="9"/>
+      <c r="AM7" s="9"/>
+      <c r="AN7" s="9"/>
+      <c r="AO7" s="9"/>
+      <c r="AP7" s="9"/>
+      <c r="AQ7" s="9"/>
     </row>
     <row r="8" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
+      <c r="A8" s="5">
         <v>5</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="16" t="s">
+      <c r="J8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L8" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M8" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N8" s="10" t="s">
+      <c r="L8" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M8" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10" t="s">
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="10"/>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10"/>
-      <c r="W8" s="10"/>
-      <c r="X8" s="10"/>
-      <c r="Y8" s="10"/>
-      <c r="Z8" s="10"/>
-      <c r="AA8" s="10"/>
-      <c r="AB8" s="10"/>
-      <c r="AC8" s="10"/>
-      <c r="AD8" s="10"/>
-      <c r="AE8" s="10"/>
-      <c r="AF8" s="10"/>
-      <c r="AG8" s="10"/>
-      <c r="AH8" s="10"/>
-      <c r="AI8" s="10"/>
-      <c r="AJ8" s="10"/>
-      <c r="AK8" s="10"/>
-      <c r="AL8" s="10"/>
-      <c r="AM8" s="10"/>
-      <c r="AN8" s="10"/>
-      <c r="AO8" s="10"/>
-      <c r="AP8" s="10"/>
-      <c r="AQ8" s="10"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="6"/>
+      <c r="AA8" s="6"/>
+      <c r="AB8" s="6"/>
+      <c r="AC8" s="6"/>
+      <c r="AD8" s="6"/>
+      <c r="AE8" s="6"/>
+      <c r="AF8" s="6"/>
+      <c r="AG8" s="6"/>
+      <c r="AH8" s="6"/>
+      <c r="AI8" s="6"/>
+      <c r="AJ8" s="6"/>
+      <c r="AK8" s="6"/>
+      <c r="AL8" s="6"/>
+      <c r="AM8" s="6"/>
+      <c r="AN8" s="6"/>
+      <c r="AO8" s="6"/>
+      <c r="AP8" s="6"/>
+      <c r="AQ8" s="6"/>
     </row>
     <row r="9" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
+      <c r="A9" s="8">
         <v>6</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="J9" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="K9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M9" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N9" s="13" t="s">
+      <c r="L9" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M9" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13" t="s">
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="13"/>
-      <c r="V9" s="13"/>
-      <c r="W9" s="13"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="13"/>
-      <c r="AB9" s="13"/>
-      <c r="AC9" s="13"/>
-      <c r="AD9" s="13"/>
-      <c r="AE9" s="13"/>
-      <c r="AF9" s="13"/>
-      <c r="AG9" s="13"/>
-      <c r="AH9" s="13"/>
-      <c r="AI9" s="13"/>
-      <c r="AJ9" s="13"/>
-      <c r="AK9" s="13"/>
-      <c r="AL9" s="13"/>
-      <c r="AM9" s="13"/>
-      <c r="AN9" s="13"/>
-      <c r="AO9" s="13"/>
-      <c r="AP9" s="13"/>
-      <c r="AQ9" s="13"/>
+      <c r="R9" s="9"/>
+      <c r="S9" s="9"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="9"/>
+      <c r="V9" s="9"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="9"/>
+      <c r="Z9" s="9"/>
+      <c r="AA9" s="9"/>
+      <c r="AB9" s="9"/>
+      <c r="AC9" s="9"/>
+      <c r="AD9" s="9"/>
+      <c r="AE9" s="9"/>
+      <c r="AF9" s="9"/>
+      <c r="AG9" s="9"/>
+      <c r="AH9" s="9"/>
+      <c r="AI9" s="9"/>
+      <c r="AJ9" s="9"/>
+      <c r="AK9" s="9"/>
+      <c r="AL9" s="9"/>
+      <c r="AM9" s="9"/>
+      <c r="AN9" s="9"/>
+      <c r="AO9" s="9"/>
+      <c r="AP9" s="9"/>
+      <c r="AQ9" s="9"/>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
+      <c r="A10" s="5">
         <v>7</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J10" s="16" t="s">
+      <c r="J10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="K10" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M10" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N10" s="10" t="s">
+      <c r="L10" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M10" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10"/>
-      <c r="X10" s="10"/>
-      <c r="Y10" s="10"/>
-      <c r="Z10" s="10"/>
-      <c r="AA10" s="10"/>
-      <c r="AB10" s="10"/>
-      <c r="AC10" s="10"/>
-      <c r="AD10" s="10"/>
-      <c r="AE10" s="10"/>
-      <c r="AF10" s="10"/>
-      <c r="AG10" s="10"/>
-      <c r="AH10" s="10"/>
-      <c r="AI10" s="10"/>
-      <c r="AJ10" s="10"/>
-      <c r="AK10" s="10"/>
-      <c r="AL10" s="10"/>
-      <c r="AM10" s="10"/>
-      <c r="AN10" s="10"/>
-      <c r="AO10" s="10"/>
-      <c r="AP10" s="10"/>
-      <c r="AQ10" s="10"/>
-    </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
+      <c r="O10" s="6"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="6"/>
+      <c r="AA10" s="6"/>
+      <c r="AB10" s="6"/>
+      <c r="AC10" s="6"/>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="6"/>
+      <c r="AF10" s="6"/>
+      <c r="AG10" s="6"/>
+      <c r="AH10" s="6"/>
+      <c r="AI10" s="6"/>
+      <c r="AJ10" s="6"/>
+      <c r="AK10" s="6"/>
+      <c r="AL10" s="6"/>
+      <c r="AM10" s="6"/>
+      <c r="AN10" s="6"/>
+      <c r="AO10" s="6"/>
+      <c r="AP10" s="6"/>
+      <c r="AQ10" s="6"/>
+    </row>
+    <row r="11" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
         <v>8</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="H11" s="12" t="s">
+      <c r="H11" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="J11" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K11" s="12" t="s">
+      <c r="K11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L11" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M11" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N11" s="13" t="s">
+      <c r="L11" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M11" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N11" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="13"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="13"/>
-      <c r="W11" s="13"/>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="13"/>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="13"/>
-      <c r="AB11" s="13"/>
-      <c r="AC11" s="13"/>
-      <c r="AD11" s="13"/>
-      <c r="AE11" s="13"/>
-      <c r="AF11" s="13"/>
-      <c r="AG11" s="13"/>
-      <c r="AH11" s="13"/>
-      <c r="AI11" s="13"/>
-      <c r="AJ11" s="13"/>
-      <c r="AK11" s="13"/>
-      <c r="AL11" s="13"/>
-      <c r="AM11" s="13"/>
-      <c r="AN11" s="13"/>
-      <c r="AO11" s="13"/>
-      <c r="AP11" s="13"/>
-      <c r="AQ11" s="13"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
+      <c r="S11" s="9"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="9"/>
+      <c r="V11" s="9"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="9"/>
+      <c r="Y11" s="9"/>
+      <c r="Z11" s="9"/>
+      <c r="AA11" s="9"/>
+      <c r="AB11" s="9"/>
+      <c r="AC11" s="9"/>
+      <c r="AD11" s="9"/>
+      <c r="AE11" s="9"/>
+      <c r="AF11" s="9"/>
+      <c r="AG11" s="9"/>
+      <c r="AH11" s="9"/>
+      <c r="AI11" s="9"/>
+      <c r="AJ11" s="9"/>
+      <c r="AK11" s="9"/>
+      <c r="AL11" s="9"/>
+      <c r="AM11" s="9"/>
+      <c r="AN11" s="9"/>
+      <c r="AO11" s="9"/>
+      <c r="AP11" s="9"/>
+      <c r="AQ11" s="9"/>
     </row>
     <row r="12" spans="1:43" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="9">
+      <c r="A12" s="5">
         <v>9</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="18" t="s">
+      <c r="I12" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J12" s="16" t="s">
+      <c r="J12" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="K12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L12" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M12" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N12" s="10" t="s">
+      <c r="L12" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M12" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10" t="s">
+      <c r="O12" s="6"/>
+      <c r="P12" s="6"/>
+      <c r="Q12" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10"/>
-      <c r="X12" s="10"/>
-      <c r="Y12" s="10"/>
-      <c r="Z12" s="10"/>
-      <c r="AA12" s="10"/>
-      <c r="AB12" s="10"/>
-      <c r="AC12" s="10"/>
-      <c r="AD12" s="10"/>
-      <c r="AE12" s="10"/>
-      <c r="AF12" s="10"/>
-      <c r="AG12" s="10"/>
-      <c r="AH12" s="10"/>
-      <c r="AI12" s="10"/>
-      <c r="AJ12" s="10"/>
-      <c r="AK12" s="10"/>
-      <c r="AL12" s="10"/>
-      <c r="AM12" s="10"/>
-      <c r="AN12" s="10"/>
-      <c r="AO12" s="10"/>
-      <c r="AP12" s="10"/>
-      <c r="AQ12" s="10"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="6"/>
+      <c r="AA12" s="6"/>
+      <c r="AB12" s="6"/>
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6"/>
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="6"/>
+      <c r="AG12" s="6"/>
+      <c r="AH12" s="6"/>
+      <c r="AI12" s="6"/>
+      <c r="AJ12" s="6"/>
+      <c r="AK12" s="6"/>
+      <c r="AL12" s="6"/>
+      <c r="AM12" s="6"/>
+      <c r="AN12" s="6"/>
+      <c r="AO12" s="6"/>
+      <c r="AP12" s="6"/>
+      <c r="AQ12" s="6"/>
     </row>
     <row r="13" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
+      <c r="A13" s="8">
         <v>10</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J13" s="16" t="s">
+      <c r="J13" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K13" s="12" t="s">
+      <c r="K13" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L13" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M13" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N13" s="13" t="s">
+      <c r="L13" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M13" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N13" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="13"/>
-      <c r="U13" s="13"/>
-      <c r="V13" s="13"/>
-      <c r="W13" s="13"/>
-      <c r="X13" s="13"/>
-      <c r="Y13" s="13"/>
-      <c r="Z13" s="13"/>
-      <c r="AA13" s="13"/>
-      <c r="AB13" s="13"/>
-      <c r="AC13" s="13"/>
-      <c r="AD13" s="13"/>
-      <c r="AE13" s="13"/>
-      <c r="AF13" s="13"/>
-      <c r="AG13" s="13"/>
-      <c r="AH13" s="13"/>
-      <c r="AI13" s="13"/>
-      <c r="AJ13" s="13"/>
-      <c r="AK13" s="13"/>
-      <c r="AL13" s="13"/>
-      <c r="AM13" s="13"/>
-      <c r="AN13" s="13"/>
-      <c r="AO13" s="13"/>
-      <c r="AP13" s="13"/>
-      <c r="AQ13" s="13"/>
-    </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A14" s="9">
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="9"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9"/>
+      <c r="V13" s="9"/>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="9"/>
+      <c r="AA13" s="9"/>
+      <c r="AB13" s="9"/>
+      <c r="AC13" s="9"/>
+      <c r="AD13" s="9"/>
+      <c r="AE13" s="9"/>
+      <c r="AF13" s="9"/>
+      <c r="AG13" s="9"/>
+      <c r="AH13" s="9"/>
+      <c r="AI13" s="9"/>
+      <c r="AJ13" s="9"/>
+      <c r="AK13" s="9"/>
+      <c r="AL13" s="9"/>
+      <c r="AM13" s="9"/>
+      <c r="AN13" s="9"/>
+      <c r="AO13" s="9"/>
+      <c r="AP13" s="9"/>
+      <c r="AQ13" s="9"/>
+    </row>
+    <row r="14" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <v>11</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="18" t="s">
+      <c r="I14" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J14" s="16" t="s">
+      <c r="J14" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K14" s="9" t="s">
+      <c r="K14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L14" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M14" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N14" s="10" t="s">
+      <c r="L14" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M14" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N14" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
-      <c r="U14" s="10"/>
-      <c r="V14" s="10"/>
-      <c r="W14" s="10"/>
-      <c r="X14" s="10"/>
-      <c r="Y14" s="10"/>
-      <c r="Z14" s="10"/>
-      <c r="AA14" s="10"/>
-      <c r="AB14" s="10"/>
-      <c r="AC14" s="10"/>
-      <c r="AD14" s="10"/>
-      <c r="AE14" s="10"/>
-      <c r="AF14" s="10"/>
-      <c r="AG14" s="10"/>
-      <c r="AH14" s="10"/>
-      <c r="AI14" s="10"/>
-      <c r="AJ14" s="10"/>
-      <c r="AK14" s="10"/>
-      <c r="AL14" s="10"/>
-      <c r="AM14" s="10"/>
-      <c r="AN14" s="10"/>
-      <c r="AO14" s="10"/>
-      <c r="AP14" s="10"/>
-      <c r="AQ14" s="10"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="6"/>
+      <c r="AF14" s="6"/>
+      <c r="AG14" s="6"/>
+      <c r="AH14" s="6"/>
+      <c r="AI14" s="6"/>
+      <c r="AJ14" s="6"/>
+      <c r="AK14" s="6"/>
+      <c r="AL14" s="6"/>
+      <c r="AM14" s="6"/>
+      <c r="AN14" s="6"/>
+      <c r="AO14" s="6"/>
+      <c r="AP14" s="6"/>
+      <c r="AQ14" s="6"/>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.3">
-      <c r="A15" s="12">
+      <c r="A15" s="8">
         <v>12</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="18" t="s">
+      <c r="I15" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K15" s="12" t="s">
+      <c r="K15" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L15" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M15" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N15" s="13" t="s">
+      <c r="L15" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M15" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N15" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
-      <c r="U15" s="13"/>
-      <c r="V15" s="13"/>
-      <c r="W15" s="13"/>
-      <c r="X15" s="13"/>
-      <c r="Y15" s="13"/>
-      <c r="Z15" s="13"/>
-      <c r="AA15" s="13"/>
-      <c r="AB15" s="13"/>
-      <c r="AC15" s="13"/>
-      <c r="AD15" s="13"/>
-      <c r="AE15" s="13"/>
-      <c r="AF15" s="13"/>
-      <c r="AG15" s="13"/>
-      <c r="AH15" s="13"/>
-      <c r="AI15" s="13"/>
-      <c r="AJ15" s="13"/>
-      <c r="AK15" s="13"/>
-      <c r="AL15" s="13"/>
-      <c r="AM15" s="13"/>
-      <c r="AN15" s="13"/>
-      <c r="AO15" s="13"/>
-      <c r="AP15" s="13"/>
-      <c r="AQ15" s="13"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+      <c r="S15" s="9"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="9"/>
+      <c r="V15" s="9"/>
+      <c r="W15" s="9"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="9"/>
+      <c r="Z15" s="9"/>
+      <c r="AA15" s="9"/>
+      <c r="AB15" s="9"/>
+      <c r="AC15" s="9"/>
+      <c r="AD15" s="9"/>
+      <c r="AE15" s="9"/>
+      <c r="AF15" s="9"/>
+      <c r="AG15" s="9"/>
+      <c r="AH15" s="9"/>
+      <c r="AI15" s="9"/>
+      <c r="AJ15" s="9"/>
+      <c r="AK15" s="9"/>
+      <c r="AL15" s="9"/>
+      <c r="AM15" s="9"/>
+      <c r="AN15" s="9"/>
+      <c r="AO15" s="9"/>
+      <c r="AP15" s="9"/>
+      <c r="AQ15" s="9"/>
     </row>
     <row r="16" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="9">
+      <c r="A16" s="5">
         <v>13</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="16" t="s">
+      <c r="J16" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K16" s="9" t="s">
+      <c r="K16" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L16" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M16" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N16" s="10" t="s">
+      <c r="L16" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M16" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10" t="s">
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
-      <c r="U16" s="10"/>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="10"/>
-      <c r="Y16" s="10"/>
-      <c r="Z16" s="10"/>
-      <c r="AA16" s="10"/>
-      <c r="AB16" s="10"/>
-      <c r="AC16" s="10"/>
-      <c r="AD16" s="10"/>
-      <c r="AE16" s="10"/>
-      <c r="AF16" s="10"/>
-      <c r="AG16" s="10"/>
-      <c r="AH16" s="10"/>
-      <c r="AI16" s="10"/>
-      <c r="AJ16" s="10"/>
-      <c r="AK16" s="10"/>
-      <c r="AL16" s="10"/>
-      <c r="AM16" s="10"/>
-      <c r="AN16" s="10"/>
-      <c r="AO16" s="10"/>
-      <c r="AP16" s="10"/>
-      <c r="AQ16" s="10"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="6"/>
+      <c r="U16" s="6"/>
+      <c r="V16" s="6"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="6"/>
+      <c r="Z16" s="6"/>
+      <c r="AA16" s="6"/>
+      <c r="AB16" s="6"/>
+      <c r="AC16" s="6"/>
+      <c r="AD16" s="6"/>
+      <c r="AE16" s="6"/>
+      <c r="AF16" s="6"/>
+      <c r="AG16" s="6"/>
+      <c r="AH16" s="6"/>
+      <c r="AI16" s="6"/>
+      <c r="AJ16" s="6"/>
+      <c r="AK16" s="6"/>
+      <c r="AL16" s="6"/>
+      <c r="AM16" s="6"/>
+      <c r="AN16" s="6"/>
+      <c r="AO16" s="6"/>
+      <c r="AP16" s="6"/>
+      <c r="AQ16" s="6"/>
     </row>
     <row r="17" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="12">
+      <c r="A17" s="8">
         <v>14</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="12" t="s">
+      <c r="H17" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="18" t="s">
+      <c r="I17" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J17" s="16" t="s">
+      <c r="J17" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K17" s="12" t="s">
+      <c r="K17" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L17" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M17" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N17" s="13" t="s">
+      <c r="L17" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M17" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N17" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="13"/>
-      <c r="V17" s="13"/>
-      <c r="W17" s="13"/>
-      <c r="X17" s="13"/>
-      <c r="Y17" s="13"/>
-      <c r="Z17" s="13"/>
-      <c r="AA17" s="13"/>
-      <c r="AB17" s="13"/>
-      <c r="AC17" s="13"/>
-      <c r="AD17" s="13"/>
-      <c r="AE17" s="13"/>
-      <c r="AF17" s="13"/>
-      <c r="AG17" s="13"/>
-      <c r="AH17" s="13"/>
-      <c r="AI17" s="13"/>
-      <c r="AJ17" s="13"/>
-      <c r="AK17" s="13"/>
-      <c r="AL17" s="13"/>
-      <c r="AM17" s="13"/>
-      <c r="AN17" s="13"/>
-      <c r="AO17" s="13"/>
-      <c r="AP17" s="13"/>
-      <c r="AQ17" s="13"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="9"/>
+      <c r="Z17" s="9"/>
+      <c r="AA17" s="9"/>
+      <c r="AB17" s="9"/>
+      <c r="AC17" s="9"/>
+      <c r="AD17" s="9"/>
+      <c r="AE17" s="9"/>
+      <c r="AF17" s="9"/>
+      <c r="AG17" s="9"/>
+      <c r="AH17" s="9"/>
+      <c r="AI17" s="9"/>
+      <c r="AJ17" s="9"/>
+      <c r="AK17" s="9"/>
+      <c r="AL17" s="9"/>
+      <c r="AM17" s="9"/>
+      <c r="AN17" s="9"/>
+      <c r="AO17" s="9"/>
+      <c r="AP17" s="9"/>
+      <c r="AQ17" s="9"/>
     </row>
     <row r="18" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="9">
+      <c r="A18" s="5">
         <v>15</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I18" s="18" t="s">
+      <c r="I18" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J18" s="16" t="s">
+      <c r="J18" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K18" s="9" t="s">
+      <c r="K18" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L18" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M18" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N18" s="10" t="s">
+      <c r="L18" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M18" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="10"/>
-      <c r="U18" s="10"/>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="10"/>
-      <c r="Y18" s="10"/>
-      <c r="Z18" s="10"/>
-      <c r="AA18" s="10"/>
-      <c r="AB18" s="10"/>
-      <c r="AC18" s="10"/>
-      <c r="AD18" s="10"/>
-      <c r="AE18" s="10"/>
-      <c r="AF18" s="10"/>
-      <c r="AG18" s="10"/>
-      <c r="AH18" s="10"/>
-      <c r="AI18" s="10"/>
-      <c r="AJ18" s="10"/>
-      <c r="AK18" s="10"/>
-      <c r="AL18" s="10"/>
-      <c r="AM18" s="10"/>
-      <c r="AN18" s="10"/>
-      <c r="AO18" s="10"/>
-      <c r="AP18" s="10"/>
-      <c r="AQ18" s="10"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="6"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="6"/>
+      <c r="AA18" s="6"/>
+      <c r="AB18" s="6"/>
+      <c r="AC18" s="6"/>
+      <c r="AD18" s="6"/>
+      <c r="AE18" s="6"/>
+      <c r="AF18" s="6"/>
+      <c r="AG18" s="6"/>
+      <c r="AH18" s="6"/>
+      <c r="AI18" s="6"/>
+      <c r="AJ18" s="6"/>
+      <c r="AK18" s="6"/>
+      <c r="AL18" s="6"/>
+      <c r="AM18" s="6"/>
+      <c r="AN18" s="6"/>
+      <c r="AO18" s="6"/>
+      <c r="AP18" s="6"/>
+      <c r="AQ18" s="6"/>
     </row>
     <row r="19" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="12">
+      <c r="A19" s="8">
         <v>16</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="G19" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I19" s="18" t="s">
+      <c r="I19" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J19" s="16" t="s">
+      <c r="J19" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K19" s="12" t="s">
+      <c r="K19" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L19" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M19" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N19" s="13" t="s">
+      <c r="L19" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M19" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N19" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="13"/>
-      <c r="U19" s="13"/>
-      <c r="V19" s="13"/>
-      <c r="W19" s="13"/>
-      <c r="X19" s="13"/>
-      <c r="Y19" s="13"/>
-      <c r="Z19" s="13"/>
-      <c r="AA19" s="13"/>
-      <c r="AB19" s="13"/>
-      <c r="AC19" s="13"/>
-      <c r="AD19" s="13"/>
-      <c r="AE19" s="13"/>
-      <c r="AF19" s="13"/>
-      <c r="AG19" s="13"/>
-      <c r="AH19" s="13"/>
-      <c r="AI19" s="13"/>
-      <c r="AJ19" s="13"/>
-      <c r="AK19" s="13"/>
-      <c r="AL19" s="13"/>
-      <c r="AM19" s="13"/>
-      <c r="AN19" s="13"/>
-      <c r="AO19" s="13"/>
-      <c r="AP19" s="13"/>
-      <c r="AQ19" s="13"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
+      <c r="S19" s="9"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="9"/>
+      <c r="V19" s="9"/>
+      <c r="W19" s="9"/>
+      <c r="X19" s="9"/>
+      <c r="Y19" s="9"/>
+      <c r="Z19" s="9"/>
+      <c r="AA19" s="9"/>
+      <c r="AB19" s="9"/>
+      <c r="AC19" s="9"/>
+      <c r="AD19" s="9"/>
+      <c r="AE19" s="9"/>
+      <c r="AF19" s="9"/>
+      <c r="AG19" s="9"/>
+      <c r="AH19" s="9"/>
+      <c r="AI19" s="9"/>
+      <c r="AJ19" s="9"/>
+      <c r="AK19" s="9"/>
+      <c r="AL19" s="9"/>
+      <c r="AM19" s="9"/>
+      <c r="AN19" s="9"/>
+      <c r="AO19" s="9"/>
+      <c r="AP19" s="9"/>
+      <c r="AQ19" s="9"/>
     </row>
     <row r="20" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="9">
+      <c r="A20" s="5">
         <v>17</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I20" s="18" t="s">
+      <c r="I20" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J20" s="16" t="s">
+      <c r="J20" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K20" s="9" t="s">
+      <c r="K20" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L20" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M20" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N20" s="10" t="s">
+      <c r="L20" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M20" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N20" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10"/>
-      <c r="S20" s="10"/>
-      <c r="T20" s="10"/>
-      <c r="U20" s="10"/>
-      <c r="V20" s="10"/>
-      <c r="W20" s="10"/>
-      <c r="X20" s="10"/>
-      <c r="Y20" s="10"/>
-      <c r="Z20" s="10"/>
-      <c r="AA20" s="10"/>
-      <c r="AB20" s="10"/>
-      <c r="AC20" s="10"/>
-      <c r="AD20" s="10"/>
-      <c r="AE20" s="10"/>
-      <c r="AF20" s="10"/>
-      <c r="AG20" s="10"/>
-      <c r="AH20" s="10"/>
-      <c r="AI20" s="10"/>
-      <c r="AJ20" s="10"/>
-      <c r="AK20" s="10"/>
-      <c r="AL20" s="10"/>
-      <c r="AM20" s="10"/>
-      <c r="AN20" s="10"/>
-      <c r="AO20" s="10"/>
-      <c r="AP20" s="10"/>
-      <c r="AQ20" s="10"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="6"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="6"/>
+      <c r="W20" s="6"/>
+      <c r="X20" s="6"/>
+      <c r="Y20" s="6"/>
+      <c r="Z20" s="6"/>
+      <c r="AA20" s="6"/>
+      <c r="AB20" s="6"/>
+      <c r="AC20" s="6"/>
+      <c r="AD20" s="6"/>
+      <c r="AE20" s="6"/>
+      <c r="AF20" s="6"/>
+      <c r="AG20" s="6"/>
+      <c r="AH20" s="6"/>
+      <c r="AI20" s="6"/>
+      <c r="AJ20" s="6"/>
+      <c r="AK20" s="6"/>
+      <c r="AL20" s="6"/>
+      <c r="AM20" s="6"/>
+      <c r="AN20" s="6"/>
+      <c r="AO20" s="6"/>
+      <c r="AP20" s="6"/>
+      <c r="AQ20" s="6"/>
     </row>
     <row r="21" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="12">
+      <c r="A21" s="8">
         <v>18</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="H21" s="12" t="s">
+      <c r="H21" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I21" s="18" t="s">
+      <c r="I21" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J21" s="16" t="s">
+      <c r="J21" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="K21" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L21" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M21" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N21" s="13" t="s">
+      <c r="L21" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M21" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N21" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O21" s="13"/>
-      <c r="P21" s="13"/>
-      <c r="Q21" s="13"/>
-      <c r="R21" s="13"/>
-      <c r="S21" s="13"/>
-      <c r="T21" s="13"/>
-      <c r="U21" s="13"/>
-      <c r="V21" s="13"/>
-      <c r="W21" s="13"/>
-      <c r="X21" s="13"/>
-      <c r="Y21" s="13"/>
-      <c r="Z21" s="13"/>
-      <c r="AA21" s="13"/>
-      <c r="AB21" s="13"/>
-      <c r="AC21" s="13"/>
-      <c r="AD21" s="13"/>
-      <c r="AE21" s="13"/>
-      <c r="AF21" s="13"/>
-      <c r="AG21" s="13"/>
-      <c r="AH21" s="13"/>
-      <c r="AI21" s="13"/>
-      <c r="AJ21" s="13"/>
-      <c r="AK21" s="13"/>
-      <c r="AL21" s="13"/>
-      <c r="AM21" s="13"/>
-      <c r="AN21" s="13"/>
-      <c r="AO21" s="13"/>
-      <c r="AP21" s="13"/>
-      <c r="AQ21" s="13"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
+      <c r="S21" s="9"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="9"/>
+      <c r="V21" s="9"/>
+      <c r="W21" s="9"/>
+      <c r="X21" s="9"/>
+      <c r="Y21" s="9"/>
+      <c r="Z21" s="9"/>
+      <c r="AA21" s="9"/>
+      <c r="AB21" s="9"/>
+      <c r="AC21" s="9"/>
+      <c r="AD21" s="9"/>
+      <c r="AE21" s="9"/>
+      <c r="AF21" s="9"/>
+      <c r="AG21" s="9"/>
+      <c r="AH21" s="9"/>
+      <c r="AI21" s="9"/>
+      <c r="AJ21" s="9"/>
+      <c r="AK21" s="9"/>
+      <c r="AL21" s="9"/>
+      <c r="AM21" s="9"/>
+      <c r="AN21" s="9"/>
+      <c r="AO21" s="9"/>
+      <c r="AP21" s="9"/>
+      <c r="AQ21" s="9"/>
     </row>
     <row r="22" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="9">
+      <c r="A22" s="5">
         <v>19</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="G22" s="10" t="s">
+      <c r="G22" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I22" s="18" t="s">
+      <c r="I22" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J22" s="16" t="s">
+      <c r="J22" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K22" s="9" t="s">
+      <c r="K22" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L22" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M22" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N22" s="10" t="s">
+      <c r="L22" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M22" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N22" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="10"/>
-      <c r="S22" s="10"/>
-      <c r="T22" s="10"/>
-      <c r="U22" s="10"/>
-      <c r="V22" s="10"/>
-      <c r="W22" s="10"/>
-      <c r="X22" s="10"/>
-      <c r="Y22" s="10"/>
-      <c r="Z22" s="10"/>
-      <c r="AA22" s="10"/>
-      <c r="AB22" s="10"/>
-      <c r="AC22" s="10"/>
-      <c r="AD22" s="10"/>
-      <c r="AE22" s="10"/>
-      <c r="AF22" s="10"/>
-      <c r="AG22" s="10"/>
-      <c r="AH22" s="10"/>
-      <c r="AI22" s="10"/>
-      <c r="AJ22" s="10"/>
-      <c r="AK22" s="10"/>
-      <c r="AL22" s="10"/>
-      <c r="AM22" s="10"/>
-      <c r="AN22" s="10"/>
-      <c r="AO22" s="10"/>
-      <c r="AP22" s="10"/>
-      <c r="AQ22" s="10"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="6"/>
+      <c r="Y22" s="6"/>
+      <c r="Z22" s="6"/>
+      <c r="AA22" s="6"/>
+      <c r="AB22" s="6"/>
+      <c r="AC22" s="6"/>
+      <c r="AD22" s="6"/>
+      <c r="AE22" s="6"/>
+      <c r="AF22" s="6"/>
+      <c r="AG22" s="6"/>
+      <c r="AH22" s="6"/>
+      <c r="AI22" s="6"/>
+      <c r="AJ22" s="6"/>
+      <c r="AK22" s="6"/>
+      <c r="AL22" s="6"/>
+      <c r="AM22" s="6"/>
+      <c r="AN22" s="6"/>
+      <c r="AO22" s="6"/>
+      <c r="AP22" s="6"/>
+      <c r="AQ22" s="6"/>
     </row>
     <row r="23" spans="1:43" ht="110.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="12">
+      <c r="A23" s="8">
         <v>20</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="F23" s="13" t="s">
+      <c r="F23" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="G23" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I23" s="18" t="s">
+      <c r="I23" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J23" s="16" t="s">
+      <c r="J23" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K23" s="12" t="s">
+      <c r="K23" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L23" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M23" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N23" s="13" t="s">
+      <c r="L23" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M23" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N23" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13"/>
-      <c r="Q23" s="13" t="s">
+      <c r="O23" s="9"/>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="R23" s="13"/>
-      <c r="S23" s="13"/>
-      <c r="T23" s="13"/>
-      <c r="U23" s="13"/>
-      <c r="V23" s="13"/>
-      <c r="W23" s="13"/>
-      <c r="X23" s="13"/>
-      <c r="Y23" s="13"/>
-      <c r="Z23" s="13"/>
-      <c r="AA23" s="13"/>
-      <c r="AB23" s="13"/>
-      <c r="AC23" s="13"/>
-      <c r="AD23" s="13"/>
-      <c r="AE23" s="13"/>
-      <c r="AF23" s="13"/>
-      <c r="AG23" s="13"/>
-      <c r="AH23" s="13"/>
-      <c r="AI23" s="13"/>
-      <c r="AJ23" s="13"/>
-      <c r="AK23" s="13"/>
-      <c r="AL23" s="13"/>
-      <c r="AM23" s="13"/>
-      <c r="AN23" s="13"/>
-      <c r="AO23" s="13"/>
-      <c r="AP23" s="13"/>
-      <c r="AQ23" s="13"/>
+      <c r="R23" s="9"/>
+      <c r="S23" s="9"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="9"/>
+      <c r="V23" s="9"/>
+      <c r="W23" s="9"/>
+      <c r="X23" s="9"/>
+      <c r="Y23" s="9"/>
+      <c r="Z23" s="9"/>
+      <c r="AA23" s="9"/>
+      <c r="AB23" s="9"/>
+      <c r="AC23" s="9"/>
+      <c r="AD23" s="9"/>
+      <c r="AE23" s="9"/>
+      <c r="AF23" s="9"/>
+      <c r="AG23" s="9"/>
+      <c r="AH23" s="9"/>
+      <c r="AI23" s="9"/>
+      <c r="AJ23" s="9"/>
+      <c r="AK23" s="9"/>
+      <c r="AL23" s="9"/>
+      <c r="AM23" s="9"/>
+      <c r="AN23" s="9"/>
+      <c r="AO23" s="9"/>
+      <c r="AP23" s="9"/>
+      <c r="AQ23" s="9"/>
     </row>
     <row r="24" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="9">
+      <c r="A24" s="5">
         <v>21</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I24" s="18" t="s">
+      <c r="I24" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J24" s="16" t="s">
+      <c r="J24" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K24" s="9" t="s">
+      <c r="K24" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L24" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M24" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N24" s="10" t="s">
+      <c r="L24" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M24" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N24" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10" t="s">
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="R24" s="10"/>
-      <c r="S24" s="10"/>
-      <c r="T24" s="10"/>
-      <c r="U24" s="10"/>
-      <c r="V24" s="10"/>
-      <c r="W24" s="10"/>
-      <c r="X24" s="10"/>
-      <c r="Y24" s="10"/>
-      <c r="Z24" s="10"/>
-      <c r="AA24" s="10"/>
-      <c r="AB24" s="10"/>
-      <c r="AC24" s="10"/>
-      <c r="AD24" s="10"/>
-      <c r="AE24" s="10"/>
-      <c r="AF24" s="10"/>
-      <c r="AG24" s="10"/>
-      <c r="AH24" s="10"/>
-      <c r="AI24" s="10"/>
-      <c r="AJ24" s="10"/>
-      <c r="AK24" s="10"/>
-      <c r="AL24" s="10"/>
-      <c r="AM24" s="10"/>
-      <c r="AN24" s="10"/>
-      <c r="AO24" s="10"/>
-      <c r="AP24" s="10"/>
-      <c r="AQ24" s="10"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="6"/>
+      <c r="T24" s="6"/>
+      <c r="U24" s="6"/>
+      <c r="V24" s="6"/>
+      <c r="W24" s="6"/>
+      <c r="X24" s="6"/>
+      <c r="Y24" s="6"/>
+      <c r="Z24" s="6"/>
+      <c r="AA24" s="6"/>
+      <c r="AB24" s="6"/>
+      <c r="AC24" s="6"/>
+      <c r="AD24" s="6"/>
+      <c r="AE24" s="6"/>
+      <c r="AF24" s="6"/>
+      <c r="AG24" s="6"/>
+      <c r="AH24" s="6"/>
+      <c r="AI24" s="6"/>
+      <c r="AJ24" s="6"/>
+      <c r="AK24" s="6"/>
+      <c r="AL24" s="6"/>
+      <c r="AM24" s="6"/>
+      <c r="AN24" s="6"/>
+      <c r="AO24" s="6"/>
+      <c r="AP24" s="6"/>
+      <c r="AQ24" s="6"/>
     </row>
     <row r="25" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="12">
+      <c r="A25" s="8">
         <v>22</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="F25" s="13" t="s">
+      <c r="F25" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G25" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="H25" s="12" t="s">
+      <c r="H25" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I25" s="18" t="s">
+      <c r="I25" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J25" s="16" t="s">
+      <c r="J25" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K25" s="12" t="s">
+      <c r="K25" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L25" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M25" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N25" s="13" t="s">
+      <c r="L25" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M25" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N25" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O25" s="13"/>
-      <c r="P25" s="13"/>
-      <c r="Q25" s="13"/>
-      <c r="R25" s="13"/>
-      <c r="S25" s="13"/>
-      <c r="T25" s="13"/>
-      <c r="U25" s="13"/>
-      <c r="V25" s="13"/>
-      <c r="W25" s="13"/>
-      <c r="X25" s="13"/>
-      <c r="Y25" s="13"/>
-      <c r="Z25" s="13"/>
-      <c r="AA25" s="13"/>
-      <c r="AB25" s="13"/>
-      <c r="AC25" s="13"/>
-      <c r="AD25" s="13"/>
-      <c r="AE25" s="13"/>
-      <c r="AF25" s="13"/>
-      <c r="AG25" s="13"/>
-      <c r="AH25" s="13"/>
-      <c r="AI25" s="13"/>
-      <c r="AJ25" s="13"/>
-      <c r="AK25" s="13"/>
-      <c r="AL25" s="13"/>
-      <c r="AM25" s="13"/>
-      <c r="AN25" s="13"/>
-      <c r="AO25" s="13"/>
-      <c r="AP25" s="13"/>
-      <c r="AQ25" s="13"/>
+      <c r="O25" s="9"/>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="9"/>
+      <c r="R25" s="9"/>
+      <c r="S25" s="9"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="9"/>
+      <c r="V25" s="9"/>
+      <c r="W25" s="9"/>
+      <c r="X25" s="9"/>
+      <c r="Y25" s="9"/>
+      <c r="Z25" s="9"/>
+      <c r="AA25" s="9"/>
+      <c r="AB25" s="9"/>
+      <c r="AC25" s="9"/>
+      <c r="AD25" s="9"/>
+      <c r="AE25" s="9"/>
+      <c r="AF25" s="9"/>
+      <c r="AG25" s="9"/>
+      <c r="AH25" s="9"/>
+      <c r="AI25" s="9"/>
+      <c r="AJ25" s="9"/>
+      <c r="AK25" s="9"/>
+      <c r="AL25" s="9"/>
+      <c r="AM25" s="9"/>
+      <c r="AN25" s="9"/>
+      <c r="AO25" s="9"/>
+      <c r="AP25" s="9"/>
+      <c r="AQ25" s="9"/>
     </row>
     <row r="26" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="9">
+      <c r="A26" s="5">
         <v>23</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="G26" s="10" t="s">
+      <c r="G26" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="I26" s="18" t="s">
+      <c r="I26" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J26" s="16" t="s">
+      <c r="J26" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K26" s="9" t="s">
+      <c r="K26" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L26" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M26" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N26" s="10" t="s">
+      <c r="L26" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M26" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N26" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="10"/>
-      <c r="S26" s="10"/>
-      <c r="T26" s="10"/>
-      <c r="U26" s="10"/>
-      <c r="V26" s="10"/>
-      <c r="W26" s="10"/>
-      <c r="X26" s="10"/>
-      <c r="Y26" s="10"/>
-      <c r="Z26" s="10"/>
-      <c r="AA26" s="10"/>
-      <c r="AB26" s="10"/>
-      <c r="AC26" s="10"/>
-      <c r="AD26" s="10"/>
-      <c r="AE26" s="10"/>
-      <c r="AF26" s="10"/>
-      <c r="AG26" s="10"/>
-      <c r="AH26" s="10"/>
-      <c r="AI26" s="10"/>
-      <c r="AJ26" s="10"/>
-      <c r="AK26" s="10"/>
-      <c r="AL26" s="10"/>
-      <c r="AM26" s="10"/>
-      <c r="AN26" s="10"/>
-      <c r="AO26" s="10"/>
-      <c r="AP26" s="10"/>
-      <c r="AQ26" s="10"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="6"/>
+      <c r="T26" s="6"/>
+      <c r="U26" s="6"/>
+      <c r="V26" s="6"/>
+      <c r="W26" s="6"/>
+      <c r="X26" s="6"/>
+      <c r="Y26" s="6"/>
+      <c r="Z26" s="6"/>
+      <c r="AA26" s="6"/>
+      <c r="AB26" s="6"/>
+      <c r="AC26" s="6"/>
+      <c r="AD26" s="6"/>
+      <c r="AE26" s="6"/>
+      <c r="AF26" s="6"/>
+      <c r="AG26" s="6"/>
+      <c r="AH26" s="6"/>
+      <c r="AI26" s="6"/>
+      <c r="AJ26" s="6"/>
+      <c r="AK26" s="6"/>
+      <c r="AL26" s="6"/>
+      <c r="AM26" s="6"/>
+      <c r="AN26" s="6"/>
+      <c r="AO26" s="6"/>
+      <c r="AP26" s="6"/>
+      <c r="AQ26" s="6"/>
     </row>
     <row r="27" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="12">
+      <c r="A27" s="8">
         <v>24</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="F27" s="13" t="s">
+      <c r="F27" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="H27" s="12" t="s">
+      <c r="H27" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="I27" s="18" t="s">
+      <c r="I27" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J27" s="16" t="s">
+      <c r="J27" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K27" s="12" t="s">
+      <c r="K27" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L27" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M27" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N27" s="13" t="s">
+      <c r="L27" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M27" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N27" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O27" s="13"/>
-      <c r="P27" s="13"/>
-      <c r="Q27" s="13"/>
-      <c r="R27" s="13"/>
-      <c r="S27" s="13"/>
-      <c r="T27" s="13"/>
-      <c r="U27" s="13"/>
-      <c r="V27" s="13"/>
-      <c r="W27" s="13"/>
-      <c r="X27" s="13"/>
-      <c r="Y27" s="13"/>
-      <c r="Z27" s="13"/>
-      <c r="AA27" s="13"/>
-      <c r="AB27" s="13"/>
-      <c r="AC27" s="13"/>
-      <c r="AD27" s="13"/>
-      <c r="AE27" s="13"/>
-      <c r="AF27" s="13"/>
-      <c r="AG27" s="13"/>
-      <c r="AH27" s="13"/>
-      <c r="AI27" s="13"/>
-      <c r="AJ27" s="13"/>
-      <c r="AK27" s="13"/>
-      <c r="AL27" s="13"/>
-      <c r="AM27" s="13"/>
-      <c r="AN27" s="13"/>
-      <c r="AO27" s="13"/>
-      <c r="AP27" s="13"/>
-      <c r="AQ27" s="13"/>
+      <c r="O27" s="9"/>
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="9"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="9"/>
+      <c r="V27" s="9"/>
+      <c r="W27" s="9"/>
+      <c r="X27" s="9"/>
+      <c r="Y27" s="9"/>
+      <c r="Z27" s="9"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="9"/>
+      <c r="AD27" s="9"/>
+      <c r="AE27" s="9"/>
+      <c r="AF27" s="9"/>
+      <c r="AG27" s="9"/>
+      <c r="AH27" s="9"/>
+      <c r="AI27" s="9"/>
+      <c r="AJ27" s="9"/>
+      <c r="AK27" s="9"/>
+      <c r="AL27" s="9"/>
+      <c r="AM27" s="9"/>
+      <c r="AN27" s="9"/>
+      <c r="AO27" s="9"/>
+      <c r="AP27" s="9"/>
+      <c r="AQ27" s="9"/>
     </row>
     <row r="28" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="9">
+      <c r="A28" s="5">
         <v>25</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="F28" s="10" t="s">
+      <c r="F28" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="G28" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="I28" s="15" t="s">
+      <c r="I28" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J28" s="16" t="s">
+      <c r="J28" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K28" s="9" t="s">
+      <c r="K28" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L28" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M28" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N28" s="10" t="s">
+      <c r="L28" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M28" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N28" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O28" s="10"/>
-      <c r="P28" s="10"/>
-      <c r="Q28" s="10"/>
-      <c r="R28" s="10"/>
-      <c r="S28" s="10"/>
-      <c r="T28" s="10"/>
-      <c r="U28" s="10"/>
-      <c r="V28" s="10"/>
-      <c r="W28" s="10"/>
-      <c r="X28" s="10"/>
-      <c r="Y28" s="10"/>
-      <c r="Z28" s="10"/>
-      <c r="AA28" s="10"/>
-      <c r="AB28" s="10"/>
-      <c r="AC28" s="10"/>
-      <c r="AD28" s="10"/>
-      <c r="AE28" s="10"/>
-      <c r="AF28" s="10"/>
-      <c r="AG28" s="10"/>
-      <c r="AH28" s="10"/>
-      <c r="AI28" s="10"/>
-      <c r="AJ28" s="10"/>
-      <c r="AK28" s="10"/>
-      <c r="AL28" s="10"/>
-      <c r="AM28" s="10"/>
-      <c r="AN28" s="10"/>
-      <c r="AO28" s="10"/>
-      <c r="AP28" s="10"/>
-      <c r="AQ28" s="10"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="6"/>
+      <c r="R28" s="6"/>
+      <c r="S28" s="6"/>
+      <c r="T28" s="6"/>
+      <c r="U28" s="6"/>
+      <c r="V28" s="6"/>
+      <c r="W28" s="6"/>
+      <c r="X28" s="6"/>
+      <c r="Y28" s="6"/>
+      <c r="Z28" s="6"/>
+      <c r="AA28" s="6"/>
+      <c r="AB28" s="6"/>
+      <c r="AC28" s="6"/>
+      <c r="AD28" s="6"/>
+      <c r="AE28" s="6"/>
+      <c r="AF28" s="6"/>
+      <c r="AG28" s="6"/>
+      <c r="AH28" s="6"/>
+      <c r="AI28" s="6"/>
+      <c r="AJ28" s="6"/>
+      <c r="AK28" s="6"/>
+      <c r="AL28" s="6"/>
+      <c r="AM28" s="6"/>
+      <c r="AN28" s="6"/>
+      <c r="AO28" s="6"/>
+      <c r="AP28" s="6"/>
+      <c r="AQ28" s="6"/>
     </row>
     <row r="29" spans="1:43" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="12">
+      <c r="A29" s="8">
         <v>26</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="F29" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="H29" s="12" t="s">
+      <c r="H29" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="I29" s="18" t="s">
+      <c r="I29" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J29" s="16" t="s">
+      <c r="J29" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K29" s="12" t="s">
+      <c r="K29" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L29" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M29" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N29" s="13" t="s">
+      <c r="L29" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M29" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N29" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O29" s="13"/>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="13" t="s">
+      <c r="O29" s="9"/>
+      <c r="P29" s="9"/>
+      <c r="Q29" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="R29" s="13"/>
-      <c r="S29" s="13"/>
-      <c r="T29" s="13"/>
-      <c r="U29" s="13"/>
-      <c r="V29" s="13"/>
-      <c r="W29" s="13"/>
-      <c r="X29" s="13"/>
-      <c r="Y29" s="13"/>
-      <c r="Z29" s="13"/>
-      <c r="AA29" s="13"/>
-      <c r="AB29" s="13"/>
-      <c r="AC29" s="13"/>
-      <c r="AD29" s="13"/>
-      <c r="AE29" s="13"/>
-      <c r="AF29" s="13"/>
-      <c r="AG29" s="13"/>
-      <c r="AH29" s="13"/>
-      <c r="AI29" s="13"/>
-      <c r="AJ29" s="13"/>
-      <c r="AK29" s="13"/>
-      <c r="AL29" s="13"/>
-      <c r="AM29" s="13"/>
-      <c r="AN29" s="13"/>
-      <c r="AO29" s="13"/>
-      <c r="AP29" s="13"/>
-      <c r="AQ29" s="13"/>
+      <c r="R29" s="9"/>
+      <c r="S29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="W29" s="9"/>
+      <c r="X29" s="9"/>
+      <c r="Y29" s="9"/>
+      <c r="Z29" s="9"/>
+      <c r="AA29" s="9"/>
+      <c r="AB29" s="9"/>
+      <c r="AC29" s="9"/>
+      <c r="AD29" s="9"/>
+      <c r="AE29" s="9"/>
+      <c r="AF29" s="9"/>
+      <c r="AG29" s="9"/>
+      <c r="AH29" s="9"/>
+      <c r="AI29" s="9"/>
+      <c r="AJ29" s="9"/>
+      <c r="AK29" s="9"/>
+      <c r="AL29" s="9"/>
+      <c r="AM29" s="9"/>
+      <c r="AN29" s="9"/>
+      <c r="AO29" s="9"/>
+      <c r="AP29" s="9"/>
+      <c r="AQ29" s="9"/>
     </row>
     <row r="30" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="9">
+      <c r="A30" s="5">
         <v>27</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="G30" s="10" t="s">
+      <c r="G30" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="I30" s="18" t="s">
+      <c r="I30" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J30" s="16" t="s">
+      <c r="J30" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K30" s="9" t="s">
+      <c r="K30" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L30" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M30" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N30" s="10" t="s">
+      <c r="L30" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M30" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N30" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O30" s="10"/>
-      <c r="P30" s="10"/>
-      <c r="Q30" s="10"/>
-      <c r="R30" s="10"/>
-      <c r="S30" s="10"/>
-      <c r="T30" s="10"/>
-      <c r="U30" s="10"/>
-      <c r="V30" s="10"/>
-      <c r="W30" s="10"/>
-      <c r="X30" s="10"/>
-      <c r="Y30" s="10"/>
-      <c r="Z30" s="10"/>
-      <c r="AA30" s="10"/>
-      <c r="AB30" s="10"/>
-      <c r="AC30" s="10"/>
-      <c r="AD30" s="10"/>
-      <c r="AE30" s="10"/>
-      <c r="AF30" s="10"/>
-      <c r="AG30" s="10"/>
-      <c r="AH30" s="10"/>
-      <c r="AI30" s="10"/>
-      <c r="AJ30" s="10"/>
-      <c r="AK30" s="10"/>
-      <c r="AL30" s="10"/>
-      <c r="AM30" s="10"/>
-      <c r="AN30" s="10"/>
-      <c r="AO30" s="10"/>
-      <c r="AP30" s="10"/>
-      <c r="AQ30" s="10"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="6"/>
+      <c r="T30" s="6"/>
+      <c r="U30" s="6"/>
+      <c r="V30" s="6"/>
+      <c r="W30" s="6"/>
+      <c r="X30" s="6"/>
+      <c r="Y30" s="6"/>
+      <c r="Z30" s="6"/>
+      <c r="AA30" s="6"/>
+      <c r="AB30" s="6"/>
+      <c r="AC30" s="6"/>
+      <c r="AD30" s="6"/>
+      <c r="AE30" s="6"/>
+      <c r="AF30" s="6"/>
+      <c r="AG30" s="6"/>
+      <c r="AH30" s="6"/>
+      <c r="AI30" s="6"/>
+      <c r="AJ30" s="6"/>
+      <c r="AK30" s="6"/>
+      <c r="AL30" s="6"/>
+      <c r="AM30" s="6"/>
+      <c r="AN30" s="6"/>
+      <c r="AO30" s="6"/>
+      <c r="AP30" s="6"/>
+      <c r="AQ30" s="6"/>
     </row>
     <row r="31" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="12">
+      <c r="A31" s="8">
         <v>28</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E31" s="13" t="s">
+      <c r="E31" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="F31" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="H31" s="12" t="s">
+      <c r="H31" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="I31" s="18" t="s">
+      <c r="I31" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J31" s="16" t="s">
+      <c r="J31" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K31" s="12" t="s">
+      <c r="K31" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L31" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M31" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N31" s="13" t="s">
+      <c r="L31" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M31" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N31" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O31" s="13"/>
-      <c r="P31" s="13"/>
-      <c r="Q31" s="13"/>
-      <c r="R31" s="13"/>
-      <c r="S31" s="13"/>
-      <c r="T31" s="13"/>
-      <c r="U31" s="13"/>
-      <c r="V31" s="13"/>
-      <c r="W31" s="13"/>
-      <c r="X31" s="13"/>
-      <c r="Y31" s="13"/>
-      <c r="Z31" s="13"/>
-      <c r="AA31" s="13"/>
-      <c r="AB31" s="13"/>
-      <c r="AC31" s="13"/>
-      <c r="AD31" s="13"/>
-      <c r="AE31" s="13"/>
-      <c r="AF31" s="13"/>
-      <c r="AG31" s="13"/>
-      <c r="AH31" s="13"/>
-      <c r="AI31" s="13"/>
-      <c r="AJ31" s="13"/>
-      <c r="AK31" s="13"/>
-      <c r="AL31" s="13"/>
-      <c r="AM31" s="13"/>
-      <c r="AN31" s="13"/>
-      <c r="AO31" s="13"/>
-      <c r="AP31" s="13"/>
-      <c r="AQ31" s="13"/>
+      <c r="O31" s="9"/>
+      <c r="P31" s="9"/>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
+      <c r="S31" s="9"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="9"/>
+      <c r="V31" s="9"/>
+      <c r="W31" s="9"/>
+      <c r="X31" s="9"/>
+      <c r="Y31" s="9"/>
+      <c r="Z31" s="9"/>
+      <c r="AA31" s="9"/>
+      <c r="AB31" s="9"/>
+      <c r="AC31" s="9"/>
+      <c r="AD31" s="9"/>
+      <c r="AE31" s="9"/>
+      <c r="AF31" s="9"/>
+      <c r="AG31" s="9"/>
+      <c r="AH31" s="9"/>
+      <c r="AI31" s="9"/>
+      <c r="AJ31" s="9"/>
+      <c r="AK31" s="9"/>
+      <c r="AL31" s="9"/>
+      <c r="AM31" s="9"/>
+      <c r="AN31" s="9"/>
+      <c r="AO31" s="9"/>
+      <c r="AP31" s="9"/>
+      <c r="AQ31" s="9"/>
     </row>
     <row r="32" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="9">
+      <c r="A32" s="5">
         <v>29</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F32" s="10" t="s">
+      <c r="F32" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="G32" s="10" t="s">
+      <c r="G32" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="H32" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="I32" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J32" s="16" t="s">
+      <c r="J32" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K32" s="9" t="s">
+      <c r="K32" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L32" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M32" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N32" s="10" t="s">
+      <c r="L32" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M32" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N32" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O32" s="10"/>
-      <c r="P32" s="10"/>
-      <c r="Q32" s="10"/>
-      <c r="R32" s="10"/>
-      <c r="S32" s="10"/>
-      <c r="T32" s="10"/>
-      <c r="U32" s="10"/>
-      <c r="V32" s="10"/>
-      <c r="W32" s="10"/>
-      <c r="X32" s="10"/>
-      <c r="Y32" s="10"/>
-      <c r="Z32" s="10"/>
-      <c r="AA32" s="10"/>
-      <c r="AB32" s="10"/>
-      <c r="AC32" s="10"/>
-      <c r="AD32" s="10"/>
-      <c r="AE32" s="10"/>
-      <c r="AF32" s="10"/>
-      <c r="AG32" s="10"/>
-      <c r="AH32" s="10"/>
-      <c r="AI32" s="10"/>
-      <c r="AJ32" s="10"/>
-      <c r="AK32" s="10"/>
-      <c r="AL32" s="10"/>
-      <c r="AM32" s="10"/>
-      <c r="AN32" s="10"/>
-      <c r="AO32" s="10"/>
-      <c r="AP32" s="10"/>
-      <c r="AQ32" s="10"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="6"/>
+      <c r="T32" s="6"/>
+      <c r="U32" s="6"/>
+      <c r="V32" s="6"/>
+      <c r="W32" s="6"/>
+      <c r="X32" s="6"/>
+      <c r="Y32" s="6"/>
+      <c r="Z32" s="6"/>
+      <c r="AA32" s="6"/>
+      <c r="AB32" s="6"/>
+      <c r="AC32" s="6"/>
+      <c r="AD32" s="6"/>
+      <c r="AE32" s="6"/>
+      <c r="AF32" s="6"/>
+      <c r="AG32" s="6"/>
+      <c r="AH32" s="6"/>
+      <c r="AI32" s="6"/>
+      <c r="AJ32" s="6"/>
+      <c r="AK32" s="6"/>
+      <c r="AL32" s="6"/>
+      <c r="AM32" s="6"/>
+      <c r="AN32" s="6"/>
+      <c r="AO32" s="6"/>
+      <c r="AP32" s="6"/>
+      <c r="AQ32" s="6"/>
     </row>
     <row r="33" spans="1:43" ht="151.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A33" s="12">
+      <c r="A33" s="8">
         <v>30</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="E33" s="13" t="s">
+      <c r="E33" s="9" t="s">
         <v>181</v>
       </c>
-      <c r="F33" s="13" t="s">
+      <c r="F33" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="H33" s="12" t="s">
+      <c r="H33" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="I33" s="18" t="s">
+      <c r="I33" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J33" s="16" t="s">
+      <c r="J33" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K33" s="12" t="s">
+      <c r="K33" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L33" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M33" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N33" s="13" t="s">
+      <c r="L33" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M33" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N33" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O33" s="13"/>
-      <c r="P33" s="13"/>
-      <c r="Q33" s="13" t="s">
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="R33" s="13"/>
-      <c r="S33" s="13"/>
-      <c r="T33" s="13"/>
-      <c r="U33" s="13"/>
-      <c r="V33" s="13"/>
-      <c r="W33" s="13"/>
-      <c r="X33" s="13"/>
-      <c r="Y33" s="13"/>
-      <c r="Z33" s="13"/>
-      <c r="AA33" s="13"/>
-      <c r="AB33" s="13"/>
-      <c r="AC33" s="13"/>
-      <c r="AD33" s="13"/>
-      <c r="AE33" s="13"/>
-      <c r="AF33" s="13"/>
-      <c r="AG33" s="13"/>
-      <c r="AH33" s="13"/>
-      <c r="AI33" s="13"/>
-      <c r="AJ33" s="13"/>
-      <c r="AK33" s="13"/>
-      <c r="AL33" s="13"/>
-      <c r="AM33" s="13"/>
-      <c r="AN33" s="13"/>
-      <c r="AO33" s="13"/>
-      <c r="AP33" s="13"/>
-      <c r="AQ33" s="13"/>
+      <c r="R33" s="9"/>
+      <c r="S33" s="9"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="9"/>
+      <c r="V33" s="9"/>
+      <c r="W33" s="9"/>
+      <c r="X33" s="9"/>
+      <c r="Y33" s="9"/>
+      <c r="Z33" s="9"/>
+      <c r="AA33" s="9"/>
+      <c r="AB33" s="9"/>
+      <c r="AC33" s="9"/>
+      <c r="AD33" s="9"/>
+      <c r="AE33" s="9"/>
+      <c r="AF33" s="9"/>
+      <c r="AG33" s="9"/>
+      <c r="AH33" s="9"/>
+      <c r="AI33" s="9"/>
+      <c r="AJ33" s="9"/>
+      <c r="AK33" s="9"/>
+      <c r="AL33" s="9"/>
+      <c r="AM33" s="9"/>
+      <c r="AN33" s="9"/>
+      <c r="AO33" s="9"/>
+      <c r="AP33" s="9"/>
+      <c r="AQ33" s="9"/>
     </row>
     <row r="34" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="9">
+      <c r="A34" s="5">
         <v>31</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="G34" s="10" t="s">
+      <c r="G34" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="I34" s="18" t="s">
+      <c r="I34" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J34" s="16" t="s">
+      <c r="J34" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K34" s="9" t="s">
+      <c r="K34" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L34" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M34" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N34" s="10" t="s">
+      <c r="L34" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M34" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N34" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O34" s="10"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10"/>
-      <c r="R34" s="10"/>
-      <c r="S34" s="10"/>
-      <c r="T34" s="10"/>
-      <c r="U34" s="10"/>
-      <c r="V34" s="10"/>
-      <c r="W34" s="10"/>
-      <c r="X34" s="10"/>
-      <c r="Y34" s="10"/>
-      <c r="Z34" s="10"/>
-      <c r="AA34" s="10"/>
-      <c r="AB34" s="10"/>
-      <c r="AC34" s="10"/>
-      <c r="AD34" s="10"/>
-      <c r="AE34" s="10"/>
-      <c r="AF34" s="10"/>
-      <c r="AG34" s="10"/>
-      <c r="AH34" s="10"/>
-      <c r="AI34" s="10"/>
-      <c r="AJ34" s="10"/>
-      <c r="AK34" s="10"/>
-      <c r="AL34" s="10"/>
-      <c r="AM34" s="10"/>
-      <c r="AN34" s="10"/>
-      <c r="AO34" s="10"/>
-      <c r="AP34" s="10"/>
-      <c r="AQ34" s="10"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6"/>
+      <c r="U34" s="6"/>
+      <c r="V34" s="6"/>
+      <c r="W34" s="6"/>
+      <c r="X34" s="6"/>
+      <c r="Y34" s="6"/>
+      <c r="Z34" s="6"/>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="6"/>
+      <c r="AC34" s="6"/>
+      <c r="AD34" s="6"/>
+      <c r="AE34" s="6"/>
+      <c r="AF34" s="6"/>
+      <c r="AG34" s="6"/>
+      <c r="AH34" s="6"/>
+      <c r="AI34" s="6"/>
+      <c r="AJ34" s="6"/>
+      <c r="AK34" s="6"/>
+      <c r="AL34" s="6"/>
+      <c r="AM34" s="6"/>
+      <c r="AN34" s="6"/>
+      <c r="AO34" s="6"/>
+      <c r="AP34" s="6"/>
+      <c r="AQ34" s="6"/>
     </row>
     <row r="35" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="12">
+      <c r="A35" s="8">
         <v>32</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="F35" s="13" t="s">
+      <c r="F35" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="G35" s="13" t="s">
+      <c r="G35" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="H35" s="12" t="s">
+      <c r="H35" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="I35" s="18" t="s">
+      <c r="I35" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J35" s="16" t="s">
+      <c r="J35" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K35" s="12" t="s">
+      <c r="K35" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L35" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M35" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N35" s="13" t="s">
+      <c r="L35" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M35" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N35" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O35" s="13"/>
-      <c r="P35" s="13"/>
-      <c r="Q35" s="13"/>
-      <c r="R35" s="13"/>
-      <c r="S35" s="13"/>
-      <c r="T35" s="13"/>
-      <c r="U35" s="13"/>
-      <c r="V35" s="13"/>
-      <c r="W35" s="13"/>
-      <c r="X35" s="13"/>
-      <c r="Y35" s="13"/>
-      <c r="Z35" s="13"/>
-      <c r="AA35" s="13"/>
-      <c r="AB35" s="13"/>
-      <c r="AC35" s="13"/>
-      <c r="AD35" s="13"/>
-      <c r="AE35" s="13"/>
-      <c r="AF35" s="13"/>
-      <c r="AG35" s="13"/>
-      <c r="AH35" s="13"/>
-      <c r="AI35" s="13"/>
-      <c r="AJ35" s="13"/>
-      <c r="AK35" s="13"/>
-      <c r="AL35" s="13"/>
-      <c r="AM35" s="13"/>
-      <c r="AN35" s="13"/>
-      <c r="AO35" s="13"/>
-      <c r="AP35" s="13"/>
-      <c r="AQ35" s="13"/>
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="9"/>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9"/>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="9"/>
+      <c r="Y35" s="9"/>
+      <c r="Z35" s="9"/>
+      <c r="AA35" s="9"/>
+      <c r="AB35" s="9"/>
+      <c r="AC35" s="9"/>
+      <c r="AD35" s="9"/>
+      <c r="AE35" s="9"/>
+      <c r="AF35" s="9"/>
+      <c r="AG35" s="9"/>
+      <c r="AH35" s="9"/>
+      <c r="AI35" s="9"/>
+      <c r="AJ35" s="9"/>
+      <c r="AK35" s="9"/>
+      <c r="AL35" s="9"/>
+      <c r="AM35" s="9"/>
+      <c r="AN35" s="9"/>
+      <c r="AO35" s="9"/>
+      <c r="AP35" s="9"/>
+      <c r="AQ35" s="9"/>
     </row>
     <row r="36" spans="1:43" ht="138" x14ac:dyDescent="0.3">
-      <c r="A36" s="9">
+      <c r="A36" s="5">
         <v>33</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="F36" s="10" t="s">
+      <c r="F36" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="G36" s="10" t="s">
+      <c r="G36" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="H36" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="I36" s="15" t="s">
+      <c r="I36" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J36" s="16" t="s">
+      <c r="J36" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K36" s="9" t="s">
+      <c r="K36" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L36" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M36" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N36" s="10" t="s">
+      <c r="L36" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M36" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N36" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O36" s="10"/>
-      <c r="P36" s="10"/>
-      <c r="Q36" s="10" t="s">
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="R36" s="10"/>
-      <c r="S36" s="10"/>
-      <c r="T36" s="10"/>
-      <c r="U36" s="10"/>
-      <c r="V36" s="10"/>
-      <c r="W36" s="10"/>
-      <c r="X36" s="10"/>
-      <c r="Y36" s="10"/>
-      <c r="Z36" s="10"/>
-      <c r="AA36" s="10"/>
-      <c r="AB36" s="10"/>
-      <c r="AC36" s="10"/>
-      <c r="AD36" s="10"/>
-      <c r="AE36" s="10"/>
-      <c r="AF36" s="10"/>
-      <c r="AG36" s="10"/>
-      <c r="AH36" s="10"/>
-      <c r="AI36" s="10"/>
-      <c r="AJ36" s="10"/>
-      <c r="AK36" s="10"/>
-      <c r="AL36" s="10"/>
-      <c r="AM36" s="10"/>
-      <c r="AN36" s="10"/>
-      <c r="AO36" s="10"/>
-      <c r="AP36" s="10"/>
-      <c r="AQ36" s="10"/>
+      <c r="R36" s="6"/>
+      <c r="S36" s="6"/>
+      <c r="T36" s="6"/>
+      <c r="U36" s="6"/>
+      <c r="V36" s="6"/>
+      <c r="W36" s="6"/>
+      <c r="X36" s="6"/>
+      <c r="Y36" s="6"/>
+      <c r="Z36" s="6"/>
+      <c r="AA36" s="6"/>
+      <c r="AB36" s="6"/>
+      <c r="AC36" s="6"/>
+      <c r="AD36" s="6"/>
+      <c r="AE36" s="6"/>
+      <c r="AF36" s="6"/>
+      <c r="AG36" s="6"/>
+      <c r="AH36" s="6"/>
+      <c r="AI36" s="6"/>
+      <c r="AJ36" s="6"/>
+      <c r="AK36" s="6"/>
+      <c r="AL36" s="6"/>
+      <c r="AM36" s="6"/>
+      <c r="AN36" s="6"/>
+      <c r="AO36" s="6"/>
+      <c r="AP36" s="6"/>
+      <c r="AQ36" s="6"/>
     </row>
     <row r="37" spans="1:43" ht="69" x14ac:dyDescent="0.3">
-      <c r="A37" s="12">
+      <c r="A37" s="8">
         <v>34</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="F37" s="9" t="s">
         <v>205</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="H37" s="12" t="s">
+      <c r="H37" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="I37" s="18" t="s">
+      <c r="I37" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J37" s="16" t="s">
+      <c r="J37" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K37" s="12" t="s">
+      <c r="K37" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L37" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M37" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N37" s="13" t="s">
+      <c r="L37" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M37" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N37" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O37" s="13"/>
-      <c r="P37" s="13"/>
-      <c r="Q37" s="13" t="s">
+      <c r="O37" s="9"/>
+      <c r="P37" s="9"/>
+      <c r="Q37" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="R37" s="13"/>
-      <c r="S37" s="13"/>
-      <c r="T37" s="13"/>
-      <c r="U37" s="13"/>
-      <c r="V37" s="13"/>
-      <c r="W37" s="13"/>
-      <c r="X37" s="13"/>
-      <c r="Y37" s="13"/>
-      <c r="Z37" s="13"/>
-      <c r="AA37" s="13"/>
-      <c r="AB37" s="13"/>
-      <c r="AC37" s="13"/>
-      <c r="AD37" s="13"/>
-      <c r="AE37" s="13"/>
-      <c r="AF37" s="13"/>
-      <c r="AG37" s="13"/>
-      <c r="AH37" s="13"/>
-      <c r="AI37" s="13"/>
-      <c r="AJ37" s="13"/>
-      <c r="AK37" s="13"/>
-      <c r="AL37" s="13"/>
-      <c r="AM37" s="13"/>
-      <c r="AN37" s="13"/>
-      <c r="AO37" s="13"/>
-      <c r="AP37" s="13"/>
-      <c r="AQ37" s="13"/>
+      <c r="R37" s="9"/>
+      <c r="S37" s="9"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="9"/>
+      <c r="V37" s="9"/>
+      <c r="W37" s="9"/>
+      <c r="X37" s="9"/>
+      <c r="Y37" s="9"/>
+      <c r="Z37" s="9"/>
+      <c r="AA37" s="9"/>
+      <c r="AB37" s="9"/>
+      <c r="AC37" s="9"/>
+      <c r="AD37" s="9"/>
+      <c r="AE37" s="9"/>
+      <c r="AF37" s="9"/>
+      <c r="AG37" s="9"/>
+      <c r="AH37" s="9"/>
+      <c r="AI37" s="9"/>
+      <c r="AJ37" s="9"/>
+      <c r="AK37" s="9"/>
+      <c r="AL37" s="9"/>
+      <c r="AM37" s="9"/>
+      <c r="AN37" s="9"/>
+      <c r="AO37" s="9"/>
+      <c r="AP37" s="9"/>
+      <c r="AQ37" s="9"/>
     </row>
     <row r="38" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="9">
+      <c r="A38" s="5">
         <v>35</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="C38" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="G38" s="10" t="s">
+      <c r="G38" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="H38" s="9" t="s">
+      <c r="H38" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="I38" s="18" t="s">
+      <c r="I38" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J38" s="16" t="s">
+      <c r="J38" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K38" s="9" t="s">
+      <c r="K38" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L38" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M38" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N38" s="10" t="s">
+      <c r="L38" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M38" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N38" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
-      <c r="R38" s="10"/>
-      <c r="S38" s="10"/>
-      <c r="T38" s="10"/>
-      <c r="U38" s="10"/>
-      <c r="V38" s="10"/>
-      <c r="W38" s="10"/>
-      <c r="X38" s="10"/>
-      <c r="Y38" s="10"/>
-      <c r="Z38" s="10"/>
-      <c r="AA38" s="10"/>
-      <c r="AB38" s="10"/>
-      <c r="AC38" s="10"/>
-      <c r="AD38" s="10"/>
-      <c r="AE38" s="10"/>
-      <c r="AF38" s="10"/>
-      <c r="AG38" s="10"/>
-      <c r="AH38" s="10"/>
-      <c r="AI38" s="10"/>
-      <c r="AJ38" s="10"/>
-      <c r="AK38" s="10"/>
-      <c r="AL38" s="10"/>
-      <c r="AM38" s="10"/>
-      <c r="AN38" s="10"/>
-      <c r="AO38" s="10"/>
-      <c r="AP38" s="10"/>
-      <c r="AQ38" s="10"/>
+      <c r="O38" s="6"/>
+      <c r="P38" s="6"/>
+      <c r="Q38" s="6"/>
+      <c r="R38" s="6"/>
+      <c r="S38" s="6"/>
+      <c r="T38" s="6"/>
+      <c r="U38" s="6"/>
+      <c r="V38" s="6"/>
+      <c r="W38" s="6"/>
+      <c r="X38" s="6"/>
+      <c r="Y38" s="6"/>
+      <c r="Z38" s="6"/>
+      <c r="AA38" s="6"/>
+      <c r="AB38" s="6"/>
+      <c r="AC38" s="6"/>
+      <c r="AD38" s="6"/>
+      <c r="AE38" s="6"/>
+      <c r="AF38" s="6"/>
+      <c r="AG38" s="6"/>
+      <c r="AH38" s="6"/>
+      <c r="AI38" s="6"/>
+      <c r="AJ38" s="6"/>
+      <c r="AK38" s="6"/>
+      <c r="AL38" s="6"/>
+      <c r="AM38" s="6"/>
+      <c r="AN38" s="6"/>
+      <c r="AO38" s="6"/>
+      <c r="AP38" s="6"/>
+      <c r="AQ38" s="6"/>
     </row>
     <row r="39" spans="1:43" ht="138" x14ac:dyDescent="0.3">
-      <c r="A39" s="12">
+      <c r="A39" s="8">
         <v>36</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="E39" s="9" t="s">
         <v>215</v>
       </c>
-      <c r="F39" s="13" t="s">
+      <c r="F39" s="9" t="s">
         <v>216</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="G39" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="H39" s="12" t="s">
+      <c r="H39" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="I39" s="15" t="s">
+      <c r="I39" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J39" s="16" t="s">
+      <c r="J39" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K39" s="12" t="s">
+      <c r="K39" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L39" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M39" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N39" s="13" t="s">
+      <c r="L39" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M39" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N39" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O39" s="13"/>
-      <c r="P39" s="13"/>
-      <c r="Q39" s="13" t="s">
+      <c r="O39" s="9"/>
+      <c r="P39" s="9"/>
+      <c r="Q39" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="R39" s="13"/>
-      <c r="S39" s="13"/>
-      <c r="T39" s="13"/>
-      <c r="U39" s="13"/>
-      <c r="V39" s="13"/>
-      <c r="W39" s="13"/>
-      <c r="X39" s="13"/>
-      <c r="Y39" s="13"/>
-      <c r="Z39" s="13"/>
-      <c r="AA39" s="13"/>
-      <c r="AB39" s="13"/>
-      <c r="AC39" s="13"/>
-      <c r="AD39" s="13"/>
-      <c r="AE39" s="13"/>
-      <c r="AF39" s="13"/>
-      <c r="AG39" s="13"/>
-      <c r="AH39" s="13"/>
-      <c r="AI39" s="13"/>
-      <c r="AJ39" s="13"/>
-      <c r="AK39" s="13"/>
-      <c r="AL39" s="13"/>
-      <c r="AM39" s="13"/>
-      <c r="AN39" s="13"/>
-      <c r="AO39" s="13"/>
-      <c r="AP39" s="13"/>
-      <c r="AQ39" s="13"/>
+      <c r="R39" s="9"/>
+      <c r="S39" s="9"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="9"/>
+      <c r="V39" s="9"/>
+      <c r="W39" s="9"/>
+      <c r="X39" s="9"/>
+      <c r="Y39" s="9"/>
+      <c r="Z39" s="9"/>
+      <c r="AA39" s="9"/>
+      <c r="AB39" s="9"/>
+      <c r="AC39" s="9"/>
+      <c r="AD39" s="9"/>
+      <c r="AE39" s="9"/>
+      <c r="AF39" s="9"/>
+      <c r="AG39" s="9"/>
+      <c r="AH39" s="9"/>
+      <c r="AI39" s="9"/>
+      <c r="AJ39" s="9"/>
+      <c r="AK39" s="9"/>
+      <c r="AL39" s="9"/>
+      <c r="AM39" s="9"/>
+      <c r="AN39" s="9"/>
+      <c r="AO39" s="9"/>
+      <c r="AP39" s="9"/>
+      <c r="AQ39" s="9"/>
     </row>
     <row r="40" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="9">
+      <c r="A40" s="5">
         <v>37</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="F40" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="G40" s="10" t="s">
+      <c r="G40" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="H40" s="9" t="s">
+      <c r="H40" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="I40" s="15" t="s">
+      <c r="I40" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J40" s="16" t="s">
+      <c r="J40" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K40" s="9" t="s">
+      <c r="K40" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L40" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M40" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N40" s="10" t="s">
+      <c r="L40" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M40" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N40" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O40" s="10"/>
-      <c r="P40" s="10"/>
-      <c r="Q40" s="10"/>
-      <c r="R40" s="10"/>
-      <c r="S40" s="10"/>
-      <c r="T40" s="10"/>
-      <c r="U40" s="10"/>
-      <c r="V40" s="10"/>
-      <c r="W40" s="10"/>
-      <c r="X40" s="10"/>
-      <c r="Y40" s="10"/>
-      <c r="Z40" s="10"/>
-      <c r="AA40" s="10"/>
-      <c r="AB40" s="10"/>
-      <c r="AC40" s="10"/>
-      <c r="AD40" s="10"/>
-      <c r="AE40" s="10"/>
-      <c r="AF40" s="10"/>
-      <c r="AG40" s="10"/>
-      <c r="AH40" s="10"/>
-      <c r="AI40" s="10"/>
-      <c r="AJ40" s="10"/>
-      <c r="AK40" s="10"/>
-      <c r="AL40" s="10"/>
-      <c r="AM40" s="10"/>
-      <c r="AN40" s="10"/>
-      <c r="AO40" s="10"/>
-      <c r="AP40" s="10"/>
-      <c r="AQ40" s="10"/>
+      <c r="O40" s="6"/>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="6"/>
+      <c r="U40" s="6"/>
+      <c r="V40" s="6"/>
+      <c r="W40" s="6"/>
+      <c r="X40" s="6"/>
+      <c r="Y40" s="6"/>
+      <c r="Z40" s="6"/>
+      <c r="AA40" s="6"/>
+      <c r="AB40" s="6"/>
+      <c r="AC40" s="6"/>
+      <c r="AD40" s="6"/>
+      <c r="AE40" s="6"/>
+      <c r="AF40" s="6"/>
+      <c r="AG40" s="6"/>
+      <c r="AH40" s="6"/>
+      <c r="AI40" s="6"/>
+      <c r="AJ40" s="6"/>
+      <c r="AK40" s="6"/>
+      <c r="AL40" s="6"/>
+      <c r="AM40" s="6"/>
+      <c r="AN40" s="6"/>
+      <c r="AO40" s="6"/>
+      <c r="AP40" s="6"/>
+      <c r="AQ40" s="6"/>
     </row>
     <row r="41" spans="1:43" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="12">
+      <c r="A41" s="8">
         <v>38</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="8" t="s">
         <v>226</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="E41" s="13" t="s">
+      <c r="E41" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="F41" s="13" t="s">
+      <c r="F41" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="G41" s="13" t="s">
+      <c r="G41" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="H41" s="12" t="s">
+      <c r="H41" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="I41" s="18" t="s">
+      <c r="I41" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J41" s="16" t="s">
+      <c r="J41" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K41" s="12" t="s">
+      <c r="K41" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L41" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M41" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N41" s="13" t="s">
+      <c r="L41" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M41" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N41" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O41" s="13"/>
-      <c r="P41" s="13"/>
-      <c r="Q41" s="13" t="s">
+      <c r="O41" s="9"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="R41" s="13"/>
-      <c r="S41" s="13"/>
-      <c r="T41" s="13"/>
-      <c r="U41" s="13"/>
-      <c r="V41" s="13"/>
-      <c r="W41" s="13"/>
-      <c r="X41" s="13"/>
-      <c r="Y41" s="13"/>
-      <c r="Z41" s="13"/>
-      <c r="AA41" s="13"/>
-      <c r="AB41" s="13"/>
-      <c r="AC41" s="13"/>
-      <c r="AD41" s="13"/>
-      <c r="AE41" s="13"/>
-      <c r="AF41" s="13"/>
-      <c r="AG41" s="13"/>
-      <c r="AH41" s="13"/>
-      <c r="AI41" s="13"/>
-      <c r="AJ41" s="13"/>
-      <c r="AK41" s="13"/>
-      <c r="AL41" s="13"/>
-      <c r="AM41" s="13"/>
-      <c r="AN41" s="13"/>
-      <c r="AO41" s="13"/>
-      <c r="AP41" s="13"/>
-      <c r="AQ41" s="13"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="9"/>
+      <c r="T41" s="9"/>
+      <c r="U41" s="9"/>
+      <c r="V41" s="9"/>
+      <c r="W41" s="9"/>
+      <c r="X41" s="9"/>
+      <c r="Y41" s="9"/>
+      <c r="Z41" s="9"/>
+      <c r="AA41" s="9"/>
+      <c r="AB41" s="9"/>
+      <c r="AC41" s="9"/>
+      <c r="AD41" s="9"/>
+      <c r="AE41" s="9"/>
+      <c r="AF41" s="9"/>
+      <c r="AG41" s="9"/>
+      <c r="AH41" s="9"/>
+      <c r="AI41" s="9"/>
+      <c r="AJ41" s="9"/>
+      <c r="AK41" s="9"/>
+      <c r="AL41" s="9"/>
+      <c r="AM41" s="9"/>
+      <c r="AN41" s="9"/>
+      <c r="AO41" s="9"/>
+      <c r="AP41" s="9"/>
+      <c r="AQ41" s="9"/>
     </row>
     <row r="42" spans="1:43" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="9">
+      <c r="A42" s="5">
         <v>39</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="G42" s="10" t="s">
+      <c r="G42" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="H42" s="9" t="s">
+      <c r="H42" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="I42" s="18" t="s">
+      <c r="I42" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J42" s="16" t="s">
+      <c r="J42" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K42" s="9" t="s">
+      <c r="K42" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L42" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M42" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N42" s="10" t="s">
+      <c r="L42" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M42" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N42" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O42" s="10"/>
-      <c r="P42" s="10"/>
-      <c r="Q42" s="10" t="s">
+      <c r="O42" s="6"/>
+      <c r="P42" s="6"/>
+      <c r="Q42" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="R42" s="10"/>
-      <c r="S42" s="10"/>
-      <c r="T42" s="10"/>
-      <c r="U42" s="10"/>
-      <c r="V42" s="10"/>
-      <c r="W42" s="10"/>
-      <c r="X42" s="10"/>
-      <c r="Y42" s="10"/>
-      <c r="Z42" s="10"/>
-      <c r="AA42" s="10"/>
-      <c r="AB42" s="10"/>
-      <c r="AC42" s="10"/>
-      <c r="AD42" s="10"/>
-      <c r="AE42" s="10"/>
-      <c r="AF42" s="10"/>
-      <c r="AG42" s="10"/>
-      <c r="AH42" s="10"/>
-      <c r="AI42" s="10"/>
-      <c r="AJ42" s="10"/>
-      <c r="AK42" s="10"/>
-      <c r="AL42" s="10"/>
-      <c r="AM42" s="10"/>
-      <c r="AN42" s="10"/>
-      <c r="AO42" s="10"/>
-      <c r="AP42" s="10"/>
-      <c r="AQ42" s="10"/>
+      <c r="R42" s="6"/>
+      <c r="S42" s="6"/>
+      <c r="T42" s="6"/>
+      <c r="U42" s="6"/>
+      <c r="V42" s="6"/>
+      <c r="W42" s="6"/>
+      <c r="X42" s="6"/>
+      <c r="Y42" s="6"/>
+      <c r="Z42" s="6"/>
+      <c r="AA42" s="6"/>
+      <c r="AB42" s="6"/>
+      <c r="AC42" s="6"/>
+      <c r="AD42" s="6"/>
+      <c r="AE42" s="6"/>
+      <c r="AF42" s="6"/>
+      <c r="AG42" s="6"/>
+      <c r="AH42" s="6"/>
+      <c r="AI42" s="6"/>
+      <c r="AJ42" s="6"/>
+      <c r="AK42" s="6"/>
+      <c r="AL42" s="6"/>
+      <c r="AM42" s="6"/>
+      <c r="AN42" s="6"/>
+      <c r="AO42" s="6"/>
+      <c r="AP42" s="6"/>
+      <c r="AQ42" s="6"/>
     </row>
     <row r="43" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="12">
+      <c r="A43" s="8">
         <v>40</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="E43" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="F43" s="13" t="s">
+      <c r="F43" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="G43" s="13" t="s">
+      <c r="G43" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="H43" s="12" t="s">
+      <c r="H43" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="I43" s="15" t="s">
+      <c r="I43" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J43" s="16" t="s">
+      <c r="J43" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K43" s="12" t="s">
+      <c r="K43" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L43" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M43" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N43" s="13" t="s">
+      <c r="L43" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M43" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N43" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O43" s="13"/>
-      <c r="P43" s="13"/>
-      <c r="Q43" s="13"/>
-      <c r="R43" s="13"/>
-      <c r="S43" s="13"/>
-      <c r="T43" s="13"/>
-      <c r="U43" s="13"/>
-      <c r="V43" s="13"/>
-      <c r="W43" s="13"/>
-      <c r="X43" s="13"/>
-      <c r="Y43" s="13"/>
-      <c r="Z43" s="13"/>
-      <c r="AA43" s="13"/>
-      <c r="AB43" s="13"/>
-      <c r="AC43" s="13"/>
-      <c r="AD43" s="13"/>
-      <c r="AE43" s="13"/>
-      <c r="AF43" s="13"/>
-      <c r="AG43" s="13"/>
-      <c r="AH43" s="13"/>
-      <c r="AI43" s="13"/>
-      <c r="AJ43" s="13"/>
-      <c r="AK43" s="13"/>
-      <c r="AL43" s="13"/>
-      <c r="AM43" s="13"/>
-      <c r="AN43" s="13"/>
-      <c r="AO43" s="13"/>
-      <c r="AP43" s="13"/>
-      <c r="AQ43" s="13"/>
+      <c r="O43" s="9"/>
+      <c r="P43" s="9"/>
+      <c r="Q43" s="9"/>
+      <c r="R43" s="9"/>
+      <c r="S43" s="9"/>
+      <c r="T43" s="9"/>
+      <c r="U43" s="9"/>
+      <c r="V43" s="9"/>
+      <c r="W43" s="9"/>
+      <c r="X43" s="9"/>
+      <c r="Y43" s="9"/>
+      <c r="Z43" s="9"/>
+      <c r="AA43" s="9"/>
+      <c r="AB43" s="9"/>
+      <c r="AC43" s="9"/>
+      <c r="AD43" s="9"/>
+      <c r="AE43" s="9"/>
+      <c r="AF43" s="9"/>
+      <c r="AG43" s="9"/>
+      <c r="AH43" s="9"/>
+      <c r="AI43" s="9"/>
+      <c r="AJ43" s="9"/>
+      <c r="AK43" s="9"/>
+      <c r="AL43" s="9"/>
+      <c r="AM43" s="9"/>
+      <c r="AN43" s="9"/>
+      <c r="AO43" s="9"/>
+      <c r="AP43" s="9"/>
+      <c r="AQ43" s="9"/>
     </row>
     <row r="44" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="9">
+      <c r="A44" s="5">
         <v>41</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F44" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="G44" s="10" t="s">
+      <c r="G44" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="H44" s="9" t="s">
+      <c r="H44" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="I44" s="15" t="s">
+      <c r="I44" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J44" s="16" t="s">
+      <c r="J44" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K44" s="9" t="s">
+      <c r="K44" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L44" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M44" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N44" s="10" t="s">
+      <c r="L44" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M44" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N44" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O44" s="10"/>
-      <c r="P44" s="10"/>
-      <c r="Q44" s="10"/>
-      <c r="R44" s="10"/>
-      <c r="S44" s="10"/>
-      <c r="T44" s="10"/>
-      <c r="U44" s="10"/>
-      <c r="V44" s="10"/>
-      <c r="W44" s="10"/>
-      <c r="X44" s="10"/>
-      <c r="Y44" s="10"/>
-      <c r="Z44" s="10"/>
-      <c r="AA44" s="10"/>
-      <c r="AB44" s="10"/>
-      <c r="AC44" s="10"/>
-      <c r="AD44" s="10"/>
-      <c r="AE44" s="10"/>
-      <c r="AF44" s="10"/>
-      <c r="AG44" s="10"/>
-      <c r="AH44" s="10"/>
-      <c r="AI44" s="10"/>
-      <c r="AJ44" s="10"/>
-      <c r="AK44" s="10"/>
-      <c r="AL44" s="10"/>
-      <c r="AM44" s="10"/>
-      <c r="AN44" s="10"/>
-      <c r="AO44" s="10"/>
-      <c r="AP44" s="10"/>
-      <c r="AQ44" s="10"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="6"/>
+      <c r="Q44" s="6"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="6"/>
+      <c r="T44" s="6"/>
+      <c r="U44" s="6"/>
+      <c r="V44" s="6"/>
+      <c r="W44" s="6"/>
+      <c r="X44" s="6"/>
+      <c r="Y44" s="6"/>
+      <c r="Z44" s="6"/>
+      <c r="AA44" s="6"/>
+      <c r="AB44" s="6"/>
+      <c r="AC44" s="6"/>
+      <c r="AD44" s="6"/>
+      <c r="AE44" s="6"/>
+      <c r="AF44" s="6"/>
+      <c r="AG44" s="6"/>
+      <c r="AH44" s="6"/>
+      <c r="AI44" s="6"/>
+      <c r="AJ44" s="6"/>
+      <c r="AK44" s="6"/>
+      <c r="AL44" s="6"/>
+      <c r="AM44" s="6"/>
+      <c r="AN44" s="6"/>
+      <c r="AO44" s="6"/>
+      <c r="AP44" s="6"/>
+      <c r="AQ44" s="6"/>
     </row>
     <row r="45" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="12">
+      <c r="A45" s="8">
         <v>42</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="E45" s="13" t="s">
+      <c r="E45" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="F45" s="13" t="s">
+      <c r="F45" s="9" t="s">
         <v>254</v>
       </c>
-      <c r="G45" s="13" t="s">
+      <c r="G45" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="H45" s="12" t="s">
+      <c r="H45" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="I45" s="18" t="s">
+      <c r="I45" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J45" s="16" t="s">
+      <c r="J45" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K45" s="12" t="s">
+      <c r="K45" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L45" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M45" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N45" s="13" t="s">
+      <c r="L45" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M45" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N45" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O45" s="13"/>
-      <c r="P45" s="13"/>
-      <c r="Q45" s="13"/>
-      <c r="R45" s="13"/>
-      <c r="S45" s="13"/>
-      <c r="T45" s="13"/>
-      <c r="U45" s="13"/>
-      <c r="V45" s="13"/>
-      <c r="W45" s="13"/>
-      <c r="X45" s="13"/>
-      <c r="Y45" s="13"/>
-      <c r="Z45" s="13"/>
-      <c r="AA45" s="13"/>
-      <c r="AB45" s="13"/>
-      <c r="AC45" s="13"/>
-      <c r="AD45" s="13"/>
-      <c r="AE45" s="13"/>
-      <c r="AF45" s="13"/>
-      <c r="AG45" s="13"/>
-      <c r="AH45" s="13"/>
-      <c r="AI45" s="13"/>
-      <c r="AJ45" s="13"/>
-      <c r="AK45" s="13"/>
-      <c r="AL45" s="13"/>
-      <c r="AM45" s="13"/>
-      <c r="AN45" s="13"/>
-      <c r="AO45" s="13"/>
-      <c r="AP45" s="13"/>
-      <c r="AQ45" s="13"/>
+      <c r="O45" s="9"/>
+      <c r="P45" s="9"/>
+      <c r="Q45" s="9"/>
+      <c r="R45" s="9"/>
+      <c r="S45" s="9"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9"/>
+      <c r="V45" s="9"/>
+      <c r="W45" s="9"/>
+      <c r="X45" s="9"/>
+      <c r="Y45" s="9"/>
+      <c r="Z45" s="9"/>
+      <c r="AA45" s="9"/>
+      <c r="AB45" s="9"/>
+      <c r="AC45" s="9"/>
+      <c r="AD45" s="9"/>
+      <c r="AE45" s="9"/>
+      <c r="AF45" s="9"/>
+      <c r="AG45" s="9"/>
+      <c r="AH45" s="9"/>
+      <c r="AI45" s="9"/>
+      <c r="AJ45" s="9"/>
+      <c r="AK45" s="9"/>
+      <c r="AL45" s="9"/>
+      <c r="AM45" s="9"/>
+      <c r="AN45" s="9"/>
+      <c r="AO45" s="9"/>
+      <c r="AP45" s="9"/>
+      <c r="AQ45" s="9"/>
     </row>
     <row r="46" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="9">
+      <c r="A46" s="5">
         <v>43</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="C46" s="10" t="s">
+      <c r="C46" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E46" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="F46" s="10" t="s">
+      <c r="F46" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="G46" s="10" t="s">
+      <c r="G46" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="H46" s="9" t="s">
+      <c r="H46" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="I46" s="18" t="s">
+      <c r="I46" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J46" s="16" t="s">
+      <c r="J46" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K46" s="9" t="s">
+      <c r="K46" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L46" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M46" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N46" s="10" t="s">
+      <c r="L46" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M46" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N46" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="10"/>
-      <c r="R46" s="10"/>
-      <c r="S46" s="10"/>
-      <c r="T46" s="10"/>
-      <c r="U46" s="10"/>
-      <c r="V46" s="10"/>
-      <c r="W46" s="10"/>
-      <c r="X46" s="10"/>
-      <c r="Y46" s="10"/>
-      <c r="Z46" s="10"/>
-      <c r="AA46" s="10"/>
-      <c r="AB46" s="10"/>
-      <c r="AC46" s="10"/>
-      <c r="AD46" s="10"/>
-      <c r="AE46" s="10"/>
-      <c r="AF46" s="10"/>
-      <c r="AG46" s="10"/>
-      <c r="AH46" s="10"/>
-      <c r="AI46" s="10"/>
-      <c r="AJ46" s="10"/>
-      <c r="AK46" s="10"/>
-      <c r="AL46" s="10"/>
-      <c r="AM46" s="10"/>
-      <c r="AN46" s="10"/>
-      <c r="AO46" s="10"/>
-      <c r="AP46" s="10"/>
-      <c r="AQ46" s="10"/>
+      <c r="O46" s="6"/>
+      <c r="P46" s="6"/>
+      <c r="Q46" s="6"/>
+      <c r="R46" s="6"/>
+      <c r="S46" s="6"/>
+      <c r="T46" s="6"/>
+      <c r="U46" s="6"/>
+      <c r="V46" s="6"/>
+      <c r="W46" s="6"/>
+      <c r="X46" s="6"/>
+      <c r="Y46" s="6"/>
+      <c r="Z46" s="6"/>
+      <c r="AA46" s="6"/>
+      <c r="AB46" s="6"/>
+      <c r="AC46" s="6"/>
+      <c r="AD46" s="6"/>
+      <c r="AE46" s="6"/>
+      <c r="AF46" s="6"/>
+      <c r="AG46" s="6"/>
+      <c r="AH46" s="6"/>
+      <c r="AI46" s="6"/>
+      <c r="AJ46" s="6"/>
+      <c r="AK46" s="6"/>
+      <c r="AL46" s="6"/>
+      <c r="AM46" s="6"/>
+      <c r="AN46" s="6"/>
+      <c r="AO46" s="6"/>
+      <c r="AP46" s="6"/>
+      <c r="AQ46" s="6"/>
     </row>
     <row r="47" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="12">
+      <c r="A47" s="8">
         <v>44</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="E47" s="13" t="s">
+      <c r="E47" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="F47" s="13" t="s">
+      <c r="F47" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="G47" s="13" t="s">
+      <c r="G47" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="H47" s="12" t="s">
+      <c r="H47" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="I47" s="18" t="s">
+      <c r="I47" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J47" s="16" t="s">
+      <c r="J47" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K47" s="12" t="s">
+      <c r="K47" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L47" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M47" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N47" s="13" t="s">
+      <c r="L47" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M47" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N47" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O47" s="13"/>
-      <c r="P47" s="13"/>
-      <c r="Q47" s="13"/>
-      <c r="R47" s="13"/>
-      <c r="S47" s="13"/>
-      <c r="T47" s="13"/>
-      <c r="U47" s="13"/>
-      <c r="V47" s="13"/>
-      <c r="W47" s="13"/>
-      <c r="X47" s="13"/>
-      <c r="Y47" s="13"/>
-      <c r="Z47" s="13"/>
-      <c r="AA47" s="13"/>
-      <c r="AB47" s="13"/>
-      <c r="AC47" s="13"/>
-      <c r="AD47" s="13"/>
-      <c r="AE47" s="13"/>
-      <c r="AF47" s="13"/>
-      <c r="AG47" s="13"/>
-      <c r="AH47" s="13"/>
-      <c r="AI47" s="13"/>
-      <c r="AJ47" s="13"/>
-      <c r="AK47" s="13"/>
-      <c r="AL47" s="13"/>
-      <c r="AM47" s="13"/>
-      <c r="AN47" s="13"/>
-      <c r="AO47" s="13"/>
-      <c r="AP47" s="13"/>
-      <c r="AQ47" s="13"/>
+      <c r="O47" s="9"/>
+      <c r="P47" s="9"/>
+      <c r="Q47" s="9"/>
+      <c r="R47" s="9"/>
+      <c r="S47" s="9"/>
+      <c r="T47" s="9"/>
+      <c r="U47" s="9"/>
+      <c r="V47" s="9"/>
+      <c r="W47" s="9"/>
+      <c r="X47" s="9"/>
+      <c r="Y47" s="9"/>
+      <c r="Z47" s="9"/>
+      <c r="AA47" s="9"/>
+      <c r="AB47" s="9"/>
+      <c r="AC47" s="9"/>
+      <c r="AD47" s="9"/>
+      <c r="AE47" s="9"/>
+      <c r="AF47" s="9"/>
+      <c r="AG47" s="9"/>
+      <c r="AH47" s="9"/>
+      <c r="AI47" s="9"/>
+      <c r="AJ47" s="9"/>
+      <c r="AK47" s="9"/>
+      <c r="AL47" s="9"/>
+      <c r="AM47" s="9"/>
+      <c r="AN47" s="9"/>
+      <c r="AO47" s="9"/>
+      <c r="AP47" s="9"/>
+      <c r="AQ47" s="9"/>
     </row>
     <row r="48" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="9">
+      <c r="A48" s="5">
         <v>45</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="D48" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="E48" s="10" t="s">
+      <c r="E48" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="F48" s="10" t="s">
+      <c r="F48" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="G48" s="10" t="s">
+      <c r="G48" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="H48" s="9" t="s">
+      <c r="H48" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="I48" s="18" t="s">
+      <c r="I48" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J48" s="16" t="s">
+      <c r="J48" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K48" s="9" t="s">
+      <c r="K48" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L48" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M48" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N48" s="10" t="s">
+      <c r="L48" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M48" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N48" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O48" s="10"/>
-      <c r="P48" s="10"/>
-      <c r="Q48" s="10"/>
-      <c r="R48" s="10"/>
-      <c r="S48" s="10"/>
-      <c r="T48" s="10"/>
-      <c r="U48" s="10"/>
-      <c r="V48" s="10"/>
-      <c r="W48" s="10"/>
-      <c r="X48" s="10"/>
-      <c r="Y48" s="10"/>
-      <c r="Z48" s="10"/>
-      <c r="AA48" s="10"/>
-      <c r="AB48" s="10"/>
-      <c r="AC48" s="10"/>
-      <c r="AD48" s="10"/>
-      <c r="AE48" s="10"/>
-      <c r="AF48" s="10"/>
-      <c r="AG48" s="10"/>
-      <c r="AH48" s="10"/>
-      <c r="AI48" s="10"/>
-      <c r="AJ48" s="10"/>
-      <c r="AK48" s="10"/>
-      <c r="AL48" s="10"/>
-      <c r="AM48" s="10"/>
-      <c r="AN48" s="10"/>
-      <c r="AO48" s="10"/>
-      <c r="AP48" s="10"/>
-      <c r="AQ48" s="10"/>
+      <c r="O48" s="6"/>
+      <c r="P48" s="6"/>
+      <c r="Q48" s="6"/>
+      <c r="R48" s="6"/>
+      <c r="S48" s="6"/>
+      <c r="T48" s="6"/>
+      <c r="U48" s="6"/>
+      <c r="V48" s="6"/>
+      <c r="W48" s="6"/>
+      <c r="X48" s="6"/>
+      <c r="Y48" s="6"/>
+      <c r="Z48" s="6"/>
+      <c r="AA48" s="6"/>
+      <c r="AB48" s="6"/>
+      <c r="AC48" s="6"/>
+      <c r="AD48" s="6"/>
+      <c r="AE48" s="6"/>
+      <c r="AF48" s="6"/>
+      <c r="AG48" s="6"/>
+      <c r="AH48" s="6"/>
+      <c r="AI48" s="6"/>
+      <c r="AJ48" s="6"/>
+      <c r="AK48" s="6"/>
+      <c r="AL48" s="6"/>
+      <c r="AM48" s="6"/>
+      <c r="AN48" s="6"/>
+      <c r="AO48" s="6"/>
+      <c r="AP48" s="6"/>
+      <c r="AQ48" s="6"/>
     </row>
     <row r="49" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="12">
+      <c r="A49" s="8">
         <v>46</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="E49" s="13" t="s">
+      <c r="E49" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="F49" s="13" t="s">
+      <c r="F49" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="G49" s="13" t="s">
+      <c r="G49" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="H49" s="12" t="s">
+      <c r="H49" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="I49" s="18" t="s">
+      <c r="I49" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J49" s="16" t="s">
+      <c r="J49" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K49" s="12" t="s">
+      <c r="K49" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L49" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M49" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N49" s="13" t="s">
+      <c r="L49" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M49" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N49" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O49" s="13"/>
-      <c r="P49" s="13"/>
-      <c r="Q49" s="13"/>
-      <c r="R49" s="13"/>
-      <c r="S49" s="13"/>
-      <c r="T49" s="13"/>
-      <c r="U49" s="13"/>
-      <c r="V49" s="13"/>
-      <c r="W49" s="13"/>
-      <c r="X49" s="13"/>
-      <c r="Y49" s="13"/>
-      <c r="Z49" s="13"/>
-      <c r="AA49" s="13"/>
-      <c r="AB49" s="13"/>
-      <c r="AC49" s="13"/>
-      <c r="AD49" s="13"/>
-      <c r="AE49" s="13"/>
-      <c r="AF49" s="13"/>
-      <c r="AG49" s="13"/>
-      <c r="AH49" s="13"/>
-      <c r="AI49" s="13"/>
-      <c r="AJ49" s="13"/>
-      <c r="AK49" s="13"/>
-      <c r="AL49" s="13"/>
-      <c r="AM49" s="13"/>
-      <c r="AN49" s="13"/>
-      <c r="AO49" s="13"/>
-      <c r="AP49" s="13"/>
-      <c r="AQ49" s="13"/>
+      <c r="O49" s="9"/>
+      <c r="P49" s="9"/>
+      <c r="Q49" s="9"/>
+      <c r="R49" s="9"/>
+      <c r="S49" s="9"/>
+      <c r="T49" s="9"/>
+      <c r="U49" s="9"/>
+      <c r="V49" s="9"/>
+      <c r="W49" s="9"/>
+      <c r="X49" s="9"/>
+      <c r="Y49" s="9"/>
+      <c r="Z49" s="9"/>
+      <c r="AA49" s="9"/>
+      <c r="AB49" s="9"/>
+      <c r="AC49" s="9"/>
+      <c r="AD49" s="9"/>
+      <c r="AE49" s="9"/>
+      <c r="AF49" s="9"/>
+      <c r="AG49" s="9"/>
+      <c r="AH49" s="9"/>
+      <c r="AI49" s="9"/>
+      <c r="AJ49" s="9"/>
+      <c r="AK49" s="9"/>
+      <c r="AL49" s="9"/>
+      <c r="AM49" s="9"/>
+      <c r="AN49" s="9"/>
+      <c r="AO49" s="9"/>
+      <c r="AP49" s="9"/>
+      <c r="AQ49" s="9"/>
     </row>
     <row r="50" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="9">
+      <c r="A50" s="5">
         <v>47</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="E50" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="F50" s="10" t="s">
+      <c r="F50" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="G50" s="10" t="s">
+      <c r="G50" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="H50" s="9" t="s">
+      <c r="H50" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="I50" s="18" t="s">
+      <c r="I50" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J50" s="16" t="s">
+      <c r="J50" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K50" s="9" t="s">
+      <c r="K50" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L50" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M50" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N50" s="10" t="s">
+      <c r="L50" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M50" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N50" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O50" s="10"/>
-      <c r="P50" s="10"/>
-      <c r="Q50" s="10"/>
-      <c r="R50" s="10"/>
-      <c r="S50" s="10"/>
-      <c r="T50" s="10"/>
-      <c r="U50" s="10"/>
-      <c r="V50" s="10"/>
-      <c r="W50" s="10"/>
-      <c r="X50" s="10"/>
-      <c r="Y50" s="10"/>
-      <c r="Z50" s="10"/>
-      <c r="AA50" s="10"/>
-      <c r="AB50" s="10"/>
-      <c r="AC50" s="10"/>
-      <c r="AD50" s="10"/>
-      <c r="AE50" s="10"/>
-      <c r="AF50" s="10"/>
-      <c r="AG50" s="10"/>
-      <c r="AH50" s="10"/>
-      <c r="AI50" s="10"/>
-      <c r="AJ50" s="10"/>
-      <c r="AK50" s="10"/>
-      <c r="AL50" s="10"/>
-      <c r="AM50" s="10"/>
-      <c r="AN50" s="10"/>
-      <c r="AO50" s="10"/>
-      <c r="AP50" s="10"/>
-      <c r="AQ50" s="10"/>
+      <c r="O50" s="6"/>
+      <c r="P50" s="6"/>
+      <c r="Q50" s="6"/>
+      <c r="R50" s="6"/>
+      <c r="S50" s="6"/>
+      <c r="T50" s="6"/>
+      <c r="U50" s="6"/>
+      <c r="V50" s="6"/>
+      <c r="W50" s="6"/>
+      <c r="X50" s="6"/>
+      <c r="Y50" s="6"/>
+      <c r="Z50" s="6"/>
+      <c r="AA50" s="6"/>
+      <c r="AB50" s="6"/>
+      <c r="AC50" s="6"/>
+      <c r="AD50" s="6"/>
+      <c r="AE50" s="6"/>
+      <c r="AF50" s="6"/>
+      <c r="AG50" s="6"/>
+      <c r="AH50" s="6"/>
+      <c r="AI50" s="6"/>
+      <c r="AJ50" s="6"/>
+      <c r="AK50" s="6"/>
+      <c r="AL50" s="6"/>
+      <c r="AM50" s="6"/>
+      <c r="AN50" s="6"/>
+      <c r="AO50" s="6"/>
+      <c r="AP50" s="6"/>
+      <c r="AQ50" s="6"/>
     </row>
     <row r="51" spans="1:43" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="12">
+      <c r="A51" s="8">
         <v>48</v>
       </c>
-      <c r="B51" s="13" t="s">
+      <c r="B51" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="13" t="s">
+      <c r="C51" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="D51" s="13" t="s">
+      <c r="D51" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="E51" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="F51" s="13" t="s">
+      <c r="F51" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="G51" s="13" t="s">
+      <c r="G51" s="9" t="s">
         <v>285</v>
       </c>
-      <c r="H51" s="12" t="s">
+      <c r="H51" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="I51" s="15" t="s">
+      <c r="I51" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J51" s="16" t="s">
+      <c r="J51" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K51" s="12" t="s">
+      <c r="K51" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L51" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M51" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N51" s="13" t="s">
+      <c r="L51" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M51" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N51" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O51" s="13"/>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="13" t="s">
+      <c r="O51" s="9"/>
+      <c r="P51" s="9"/>
+      <c r="Q51" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="R51" s="13"/>
-      <c r="S51" s="13"/>
-      <c r="T51" s="13"/>
-      <c r="U51" s="13"/>
-      <c r="V51" s="13"/>
-      <c r="W51" s="13"/>
-      <c r="X51" s="13"/>
-      <c r="Y51" s="13"/>
-      <c r="Z51" s="13"/>
-      <c r="AA51" s="13"/>
-      <c r="AB51" s="13"/>
-      <c r="AC51" s="13"/>
-      <c r="AD51" s="13"/>
-      <c r="AE51" s="13"/>
-      <c r="AF51" s="13"/>
-      <c r="AG51" s="13"/>
-      <c r="AH51" s="13"/>
-      <c r="AI51" s="13"/>
-      <c r="AJ51" s="13"/>
-      <c r="AK51" s="13"/>
-      <c r="AL51" s="13"/>
-      <c r="AM51" s="13"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51" s="13"/>
-      <c r="AQ51" s="13"/>
+      <c r="R51" s="9"/>
+      <c r="S51" s="9"/>
+      <c r="T51" s="9"/>
+      <c r="U51" s="9"/>
+      <c r="V51" s="9"/>
+      <c r="W51" s="9"/>
+      <c r="X51" s="9"/>
+      <c r="Y51" s="9"/>
+      <c r="Z51" s="9"/>
+      <c r="AA51" s="9"/>
+      <c r="AB51" s="9"/>
+      <c r="AC51" s="9"/>
+      <c r="AD51" s="9"/>
+      <c r="AE51" s="9"/>
+      <c r="AF51" s="9"/>
+      <c r="AG51" s="9"/>
+      <c r="AH51" s="9"/>
+      <c r="AI51" s="9"/>
+      <c r="AJ51" s="9"/>
+      <c r="AK51" s="9"/>
+      <c r="AL51" s="9"/>
+      <c r="AM51" s="9"/>
+      <c r="AN51" s="9"/>
+      <c r="AO51" s="9"/>
+      <c r="AP51" s="9"/>
+      <c r="AQ51" s="9"/>
     </row>
     <row r="52" spans="1:43" ht="69" x14ac:dyDescent="0.3">
-      <c r="A52" s="9">
+      <c r="A52" s="5">
         <v>49</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C52" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="D52" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="F52" s="10" t="s">
+      <c r="F52" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="G52" s="10" t="s">
+      <c r="G52" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="H52" s="9" t="s">
+      <c r="H52" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="I52" s="15" t="s">
+      <c r="I52" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J52" s="16" t="s">
+      <c r="J52" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K52" s="9" t="s">
+      <c r="K52" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="L52" s="11">
-        <v>46227</v>
-      </c>
-      <c r="M52" s="11">
-        <v>46227</v>
-      </c>
-      <c r="N52" s="10" t="s">
+      <c r="L52" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M52" s="7">
+        <v>46227</v>
+      </c>
+      <c r="N52" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="O52" s="10"/>
-      <c r="P52" s="10"/>
-      <c r="Q52" s="10" t="s">
+      <c r="O52" s="6"/>
+      <c r="P52" s="6"/>
+      <c r="Q52" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="R52" s="10"/>
-      <c r="S52" s="10"/>
-      <c r="T52" s="10"/>
-      <c r="U52" s="10"/>
-      <c r="V52" s="10"/>
-      <c r="W52" s="10"/>
-      <c r="X52" s="10"/>
-      <c r="Y52" s="10"/>
-      <c r="Z52" s="10"/>
-      <c r="AA52" s="10"/>
-      <c r="AB52" s="10"/>
-      <c r="AC52" s="10"/>
-      <c r="AD52" s="10"/>
-      <c r="AE52" s="10"/>
-      <c r="AF52" s="10"/>
-      <c r="AG52" s="10"/>
-      <c r="AH52" s="10"/>
-      <c r="AI52" s="10"/>
-      <c r="AJ52" s="10"/>
-      <c r="AK52" s="10"/>
-      <c r="AL52" s="10"/>
-      <c r="AM52" s="10"/>
-      <c r="AN52" s="10"/>
-      <c r="AO52" s="10"/>
-      <c r="AP52" s="10"/>
-      <c r="AQ52" s="10"/>
+      <c r="R52" s="6"/>
+      <c r="S52" s="6"/>
+      <c r="T52" s="6"/>
+      <c r="U52" s="6"/>
+      <c r="V52" s="6"/>
+      <c r="W52" s="6"/>
+      <c r="X52" s="6"/>
+      <c r="Y52" s="6"/>
+      <c r="Z52" s="6"/>
+      <c r="AA52" s="6"/>
+      <c r="AB52" s="6"/>
+      <c r="AC52" s="6"/>
+      <c r="AD52" s="6"/>
+      <c r="AE52" s="6"/>
+      <c r="AF52" s="6"/>
+      <c r="AG52" s="6"/>
+      <c r="AH52" s="6"/>
+      <c r="AI52" s="6"/>
+      <c r="AJ52" s="6"/>
+      <c r="AK52" s="6"/>
+      <c r="AL52" s="6"/>
+      <c r="AM52" s="6"/>
+      <c r="AN52" s="6"/>
+      <c r="AO52" s="6"/>
+      <c r="AP52" s="6"/>
+      <c r="AQ52" s="6"/>
     </row>
     <row r="53" spans="1:43" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A53" s="12">
+      <c r="A53" s="8">
         <v>50</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="D53" s="13" t="s">
+      <c r="D53" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="E53" s="13" t="s">
+      <c r="E53" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="F53" s="13" t="s">
+      <c r="F53" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="G53" s="13" t="s">
+      <c r="G53" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="H53" s="12" t="s">
+      <c r="H53" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="I53" s="15" t="s">
+      <c r="I53" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J53" s="16" t="s">
+      <c r="J53" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K53" s="12" t="s">
+      <c r="K53" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="L53" s="14">
-        <v>46227</v>
-      </c>
-      <c r="M53" s="14">
-        <v>46227</v>
-      </c>
-      <c r="N53" s="13" t="s">
+      <c r="L53" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M53" s="10">
+        <v>46227</v>
+      </c>
+      <c r="N53" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="O53" s="13"/>
-      <c r="P53" s="13"/>
-      <c r="Q53" s="13" t="s">
+      <c r="O53" s="9"/>
+      <c r="P53" s="9"/>
+      <c r="Q53" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="R53" s="13"/>
-      <c r="S53" s="13"/>
-      <c r="T53" s="13"/>
-      <c r="U53" s="13"/>
-      <c r="V53" s="13"/>
-      <c r="W53" s="13"/>
-      <c r="X53" s="13"/>
-      <c r="Y53" s="13"/>
-      <c r="Z53" s="13"/>
-      <c r="AA53" s="13"/>
-      <c r="AB53" s="13"/>
-      <c r="AC53" s="13"/>
-      <c r="AD53" s="13"/>
-      <c r="AE53" s="13"/>
-      <c r="AF53" s="13"/>
-      <c r="AG53" s="13"/>
-      <c r="AH53" s="13"/>
-      <c r="AI53" s="13"/>
-      <c r="AJ53" s="13"/>
-      <c r="AK53" s="13"/>
-      <c r="AL53" s="13"/>
-      <c r="AM53" s="13"/>
-      <c r="AN53" s="13"/>
-      <c r="AO53" s="13"/>
-      <c r="AP53" s="13"/>
-      <c r="AQ53" s="13"/>
+      <c r="R53" s="9"/>
+      <c r="S53" s="9"/>
+      <c r="T53" s="9"/>
+      <c r="U53" s="9"/>
+      <c r="V53" s="9"/>
+      <c r="W53" s="9"/>
+      <c r="X53" s="9"/>
+      <c r="Y53" s="9"/>
+      <c r="Z53" s="9"/>
+      <c r="AA53" s="9"/>
+      <c r="AB53" s="9"/>
+      <c r="AC53" s="9"/>
+      <c r="AD53" s="9"/>
+      <c r="AE53" s="9"/>
+      <c r="AF53" s="9"/>
+      <c r="AG53" s="9"/>
+      <c r="AH53" s="9"/>
+      <c r="AI53" s="9"/>
+      <c r="AJ53" s="9"/>
+      <c r="AK53" s="9"/>
+      <c r="AL53" s="9"/>
+      <c r="AM53" s="9"/>
+      <c r="AN53" s="9"/>
+      <c r="AO53" s="9"/>
+      <c r="AP53" s="9"/>
+      <c r="AQ53" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:AQ53" xr:uid="{3F705807-3751-4CC0-9EC5-D598C44B33ED}"/>
@@ -5451,86 +5455,86 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>299</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="15" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="16">
         <v>24</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="17">
         <v>0.48</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="16" t="s">
         <v>240</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="16">
         <v>11</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="17">
         <v>0.22</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="16">
         <v>15</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="17">
         <v>0.3</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="18">
         <v>50</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="19">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="2" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="C10" s="7"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="21">
+      <c r="B11" s="16">
         <v>50</v>
       </c>
     </row>

--- a/DMA350_Testlist_Report.xlsx
+++ b/DMA350_Testlist_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83377f57b735e897/Máy tính/DMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{2625DCD3-86CB-454F-AA68-A012DEAA1CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E45DFA8-0294-46C0-B692-ECDF5AA7947D}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{2625DCD3-86CB-454F-AA68-A012DEAA1CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F8C427E-4EEE-4AB2-862A-D1C8A4680722}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5EF85DA-40B8-41A9-8419-62FC068EFE4F}"/>
   </bookViews>
@@ -1224,6 +1224,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1958,7 +1962,7 @@
       <c r="AP6" s="6"/>
       <c r="AQ6" s="6"/>
     </row>
-    <row r="7" spans="1:43" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:43" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>4</v>
       </c>
@@ -2329,7 +2333,7 @@
       <c r="AP11" s="9"/>
       <c r="AQ11" s="9"/>
     </row>
-    <row r="12" spans="1:43" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:43" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>9</v>
       </c>
@@ -3136,7 +3140,7 @@
       <c r="AP22" s="6"/>
       <c r="AQ22" s="6"/>
     </row>
-    <row r="23" spans="1:43" ht="110.4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>20</v>
       </c>
@@ -3211,7 +3215,7 @@
       <c r="AP23" s="9"/>
       <c r="AQ23" s="9"/>
     </row>
-    <row r="24" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>21</v>
       </c>
@@ -3578,7 +3582,7 @@
       <c r="AP28" s="6"/>
       <c r="AQ28" s="6"/>
     </row>
-    <row r="29" spans="1:43" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>26</v>
       </c>
@@ -3872,7 +3876,7 @@
       <c r="AP32" s="6"/>
       <c r="AQ32" s="6"/>
     </row>
-    <row r="33" spans="1:43" ht="151.80000000000001" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>30</v>
       </c>
@@ -4093,7 +4097,7 @@
       <c r="AP35" s="9"/>
       <c r="AQ35" s="9"/>
     </row>
-    <row r="36" spans="1:43" ht="138" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>33</v>
       </c>
@@ -4168,7 +4172,7 @@
       <c r="AP36" s="6"/>
       <c r="AQ36" s="6"/>
     </row>
-    <row r="37" spans="1:43" ht="69" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>34</v>
       </c>
@@ -4316,7 +4320,7 @@
       <c r="AP38" s="6"/>
       <c r="AQ38" s="6"/>
     </row>
-    <row r="39" spans="1:43" ht="138" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>36</v>
       </c>
@@ -4464,7 +4468,7 @@
       <c r="AP40" s="6"/>
       <c r="AQ40" s="6"/>
     </row>
-    <row r="41" spans="1:43" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>38</v>
       </c>
@@ -4539,7 +4543,7 @@
       <c r="AP41" s="9"/>
       <c r="AQ41" s="9"/>
     </row>
-    <row r="42" spans="1:43" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>39</v>
       </c>
@@ -5198,7 +5202,7 @@
       <c r="AP50" s="6"/>
       <c r="AQ50" s="6"/>
     </row>
-    <row r="51" spans="1:43" ht="124.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>48</v>
       </c>
@@ -5273,7 +5277,7 @@
       <c r="AP51" s="9"/>
       <c r="AQ51" s="9"/>
     </row>
-    <row r="52" spans="1:43" ht="69" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>49</v>
       </c>
@@ -5348,7 +5352,7 @@
       <c r="AP52" s="6"/>
       <c r="AQ52" s="6"/>
     </row>
-    <row r="53" spans="1:43" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>50</v>
       </c>

--- a/DMA350_Testlist_Report.xlsx
+++ b/DMA350_Testlist_Report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83377f57b735e897/Máy tính/DMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{2625DCD3-86CB-454F-AA68-A012DEAA1CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F8C427E-4EEE-4AB2-862A-D1C8A4680722}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{2625DCD3-86CB-454F-AA68-A012DEAA1CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82F9067E-796E-4843-9AE8-260C5C380D06}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5EF85DA-40B8-41A9-8419-62FC068EFE4F}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Summary" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test List'!$A$3:$AQ$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test List'!$A$3:$AP$53</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="254">
   <si>
     <t>DMA-350 DMAC - TEST LIST REPORT (UVM Verification)</t>
   </si>
@@ -54,9 +54,6 @@
     <t>No.</t>
   </si>
   <si>
-    <t>Test ID</t>
-  </si>
-  <si>
     <t>Feature Group</t>
   </si>
   <si>
@@ -102,9 +99,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>DMA-1D-001</t>
-  </si>
-  <si>
     <t>1D Transfer</t>
   </si>
   <si>
@@ -138,9 +132,6 @@
     <t>Basic 1D happy path.</t>
   </si>
   <si>
-    <t>DMA-1D-002</t>
-  </si>
-  <si>
     <t>dma350_1d_single_wrap_test</t>
   </si>
   <si>
@@ -156,9 +147,6 @@
     <t>TRM 5.2.2</t>
   </si>
   <si>
-    <t>DMA-1D-003</t>
-  </si>
-  <si>
     <t>dma350_1d_single_fill_test</t>
   </si>
   <si>
@@ -171,9 +159,6 @@
     <t>32 words = FILLVAL written to destination; no read transaction; DONE=1; no error.</t>
   </si>
   <si>
-    <t>DMA-1D-004</t>
-  </si>
-  <si>
     <t>dma350_1d_single_src0_des0_cont_test</t>
   </si>
   <si>
@@ -192,9 +177,6 @@
     <t>Edge case - no transfer expected.</t>
   </si>
   <si>
-    <t>DMA-1D-005</t>
-  </si>
-  <si>
     <t>dma350_1d_single_src0_des0_wrap_test</t>
   </si>
   <si>
@@ -210,9 +192,6 @@
     <t>Edge case.</t>
   </si>
   <si>
-    <t>DMA-1D-006</t>
-  </si>
-  <si>
     <t>dma350_1d_single_src0_des0_fill_test</t>
   </si>
   <si>
@@ -222,9 +201,6 @@
     <t>SRC=0; DES=0; XTYPE=fill; expect_idle=1</t>
   </si>
   <si>
-    <t>DMA-1D-007</t>
-  </si>
-  <si>
     <t>dma350_1d_single_src0_desgt_cont_test</t>
   </si>
   <si>
@@ -240,9 +216,6 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>DMA-1D-008</t>
-  </si>
-  <si>
     <t>dma350_1d_single_src0_desgt_wrap_test</t>
   </si>
   <si>
@@ -255,9 +228,6 @@
     <t>Nothing happens: no read or write; no error.</t>
   </si>
   <si>
-    <t>DMA-1D-009</t>
-  </si>
-  <si>
     <t>dma350_1d_single_src0_desgt_fill_test</t>
   </si>
   <si>
@@ -273,9 +243,6 @@
     <t>Fill covers destination even with empty source.</t>
   </si>
   <si>
-    <t>DMA-1D-010</t>
-  </si>
-  <si>
     <t>dma350_1d_single_srcgt_des0_cont_test</t>
   </si>
   <si>
@@ -288,9 +255,6 @@
     <t>No write; only SRCXSIZE reads issued (typical stream output); SRCXSIZE=0 at end.</t>
   </si>
   <si>
-    <t>DMA-1D-011</t>
-  </si>
-  <si>
     <t>dma350_1d_single_srcgt_des0_wrap_test</t>
   </si>
   <si>
@@ -303,9 +267,6 @@
     <t>No write; only SRCXSIZE reads issued; SRCXSIZE=0 at end.</t>
   </si>
   <si>
-    <t>DMA-1D-012</t>
-  </si>
-  <si>
     <t>dma350_1d_single_srcgt_des0_fill_test</t>
   </si>
   <si>
@@ -315,9 +276,6 @@
     <t>SRC=16; DES=0; XTYPE=fill; chk_src_drained=1</t>
   </si>
   <si>
-    <t>DMA-1D-013</t>
-  </si>
-  <si>
     <t>dma350_1d_single_src_eq_des_cont_test</t>
   </si>
   <si>
@@ -333,9 +291,6 @@
     <t>Balanced baseline case.</t>
   </si>
   <si>
-    <t>DMA-1D-014</t>
-  </si>
-  <si>
     <t>dma350_1d_single_src_eq_des_wrap_test</t>
   </si>
   <si>
@@ -348,9 +303,6 @@
     <t>Normal 1D operation regardless of XTYPE; both drained; no error.</t>
   </si>
   <si>
-    <t>DMA-1D-015</t>
-  </si>
-  <si>
     <t>dma350_1d_single_src_eq_des_fill_test</t>
   </si>
   <si>
@@ -360,9 +312,6 @@
     <t>SRC=DES=16; XTYPE=fill; chk_src_drained=1; chk_des_drained=1</t>
   </si>
   <si>
-    <t>DMA-1D-016</t>
-  </si>
-  <si>
     <t>dma350_1d_single_src_gt_des_cont_test</t>
   </si>
   <si>
@@ -375,9 +324,6 @@
     <t>Destination too small -&gt; copy stops when des full; surplus data dropped in DMAC, NOT overwritten; DESXSIZE=0.</t>
   </si>
   <si>
-    <t>DMA-1D-017</t>
-  </si>
-  <si>
     <t>dma350_1d_single_src_gt_des_wrap_test</t>
   </si>
   <si>
@@ -390,9 +336,6 @@
     <t>Destination too small -&gt; copy stops when des full; surplus dropped, NOT overwritten.</t>
   </si>
   <si>
-    <t>DMA-1D-018</t>
-  </si>
-  <si>
     <t>dma350_1d_single_src_gt_des_fill_test</t>
   </si>
   <si>
@@ -402,9 +345,6 @@
     <t>SRC=16; DES=8; XTYPE=fill; chk_des_drained=1</t>
   </si>
   <si>
-    <t>DMA-1D-019</t>
-  </si>
-  <si>
     <t>dma350_1d_single_src_lt_des_cont_test</t>
   </si>
   <si>
@@ -417,9 +357,6 @@
     <t>Source runs out -&gt; DMAC stops; SRCXSIZE reads and SRCXSIZE writes; SRCXSIZE=0.</t>
   </si>
   <si>
-    <t>DMA-1D-020</t>
-  </si>
-  <si>
     <t>dma350_1d_single_src_lt_des_wrap_test</t>
   </si>
   <si>
@@ -435,9 +372,6 @@
     <t>Cannot use SRCXSIZE/SRCADDR to infer reads performed.</t>
   </si>
   <si>
-    <t>DMA-1D-021</t>
-  </si>
-  <si>
     <t>dma350_1d_single_src_lt_des_fill_test</t>
   </si>
   <si>
@@ -453,9 +387,6 @@
     <t>Copy head + fill tail.</t>
   </si>
   <si>
-    <t>DMA-1D-022</t>
-  </si>
-  <si>
     <t>dma350_1d_single_desinc0_cont_test</t>
   </si>
   <si>
@@ -468,9 +399,6 @@
     <t>DESXADDRINC=0 (FIFO): source runs out -&gt; stop; SRCXSIZE reads and SRCXSIZE writes.</t>
   </si>
   <si>
-    <t>DMA-1D-023</t>
-  </si>
-  <si>
     <t>dma350_1d_single_desinc0_wrap_test</t>
   </si>
   <si>
@@ -483,9 +411,6 @@
     <t>DESXADDRINC=0: destination address does not advance so no real wrap; source repeated into FIFO -&gt; des_data[i]=src_data[i%3].</t>
   </si>
   <si>
-    <t>DMA-1D-024</t>
-  </si>
-  <si>
     <t>dma350_1d_single_desinc0_fill_test</t>
   </si>
   <si>
@@ -498,9 +423,6 @@
     <t>DESXADDRINC=0: fill value written into FIFO at end of transfer.</t>
   </si>
   <si>
-    <t>DMA-TRG-001</t>
-  </si>
-  <si>
     <t>Trigger</t>
   </si>
   <si>
@@ -519,9 +441,6 @@
     <t>TRM 5.4</t>
   </si>
   <si>
-    <t>DMA-TRG-002</t>
-  </si>
-  <si>
     <t>dma350_trig_srccmd_last_single_test</t>
   </si>
   <si>
@@ -537,9 +456,6 @@
     <t>LAST only changes pin encoding, not item count.</t>
   </si>
   <si>
-    <t>DMA-TRG-003</t>
-  </si>
-  <si>
     <t>dma350_trig_srccmd_block_test</t>
   </si>
   <si>
@@ -552,9 +468,6 @@
     <t>COMMAND mode: 1 trigger releases whole command regardless of reqtype=BLOCK; DMAC acks correctly; completes.</t>
   </si>
   <si>
-    <t>DMA-TRG-004</t>
-  </si>
-  <si>
     <t>dma350_trig_srccmd_last_block_test</t>
   </si>
   <si>
@@ -567,9 +480,6 @@
     <t>1 trigger = whole command; DMAC acks LAST_OKAY; completes.</t>
   </si>
   <si>
-    <t>DMA-TRG-005</t>
-  </si>
-  <si>
     <t>dma350_trig_srcflow_single_test</t>
   </si>
   <si>
@@ -582,9 +492,6 @@
     <t>Each SINGLE = 1 credit = 1 item; supplying xsize=16 triggers auto-ends the command; no LAST needed.</t>
   </si>
   <si>
-    <t>DMA-TRG-006</t>
-  </si>
-  <si>
     <t>dma350_trig_srcflow_last_single_test</t>
   </si>
   <si>
@@ -600,9 +507,6 @@
     <t>Must supply full credit before LAST to avoid early close (false scoreboard fail).</t>
   </si>
   <si>
-    <t>DMA-TRG-007</t>
-  </si>
-  <si>
     <t>dma350_trig_srcflow_block_test</t>
   </si>
   <si>
@@ -615,9 +519,6 @@
     <t>Each BLOCK = (BLKSIZE+1)=4 credits; supplying xsize/(blk+1)=4 triggers auto-ends the command.</t>
   </si>
   <si>
-    <t>DMA-TRG-008</t>
-  </si>
-  <si>
     <t>dma350_trig_srcflow_last_block_test</t>
   </si>
   <si>
@@ -630,9 +531,6 @@
     <t>3 BLOCK (12 items) + 1 LAST_BLOCK (4 items) = exactly 16; LAST_BLOCK closes command; completes.</t>
   </si>
   <si>
-    <t>DMA-TRG-009</t>
-  </si>
-  <si>
     <t>dma350_trig_bothcmd_test</t>
   </si>
   <si>
@@ -651,9 +549,6 @@
     <t>Key check: DMAC waits for BOTH reqs before starting the command.</t>
   </si>
   <si>
-    <t>DMA-TRG-010</t>
-  </si>
-  <si>
     <t>dma350_trig_srcflow_descmd_test</t>
   </si>
   <si>
@@ -669,9 +564,6 @@
     <t>Total SRC credit must equal xsize.</t>
   </si>
   <si>
-    <t>DMA-TRG-011</t>
-  </si>
-  <si>
     <t>dma350_trig_srccmd_desblock_test</t>
   </si>
   <si>
@@ -684,9 +576,6 @@
     <t>SRC 1 trigger starts the read; DES BLOCK + LAST_BLOCK stream grants writes per block; completes.</t>
   </si>
   <si>
-    <t>DMA-TRG-012</t>
-  </si>
-  <si>
     <t>dma350_trig_internal_test</t>
   </si>
   <si>
@@ -705,9 +594,6 @@
     <t>RTL forces TRIGMODE=CMD when TYPE=INTERNAL; SEL is the source channel number.</t>
   </si>
   <si>
-    <t>DMA-TRG-013</t>
-  </si>
-  <si>
     <t>dma350_trig_sw_src_test</t>
   </si>
   <si>
@@ -723,9 +609,6 @@
     <t>TRM 5.4.3</t>
   </si>
   <si>
-    <t>DMA-TRG-014</t>
-  </si>
-  <si>
     <t>dma350_trig_sw_des_test</t>
   </si>
   <si>
@@ -741,9 +624,6 @@
     <t>Destination trigger: destination peripheral paces the writes.</t>
   </si>
   <si>
-    <t>DMA-TRG-015</t>
-  </si>
-  <si>
     <t>dma350_trig_sw_trigout_ack_test</t>
   </si>
   <si>
@@ -762,9 +642,6 @@
     <t>Requires disabling trig_agt_t0 trigout_auto_ack via config_db.</t>
   </si>
   <si>
-    <t>DMA-CL-001</t>
-  </si>
-  <si>
     <t>Command Linking</t>
   </si>
   <si>
@@ -783,9 +660,6 @@
     <t>TRM 5.7</t>
   </si>
   <si>
-    <t>DMA-CL-002</t>
-  </si>
-  <si>
     <t>dma350_cmdlink_apb_3cmd_test</t>
   </si>
   <si>
@@ -798,9 +672,6 @@
     <t>Three commands loaded &amp; executed per header; chain ends ENABLECMD=0; no error.</t>
   </si>
   <si>
-    <t>DMA-CL-003</t>
-  </si>
-  <si>
     <t>dma350_cmdlink_apb_regclear_test</t>
   </si>
   <si>
@@ -813,9 +684,6 @@
     <t>Header REGCLEAR bit loaded correctly; old config wiped, new config applied; chain completes.</t>
   </si>
   <si>
-    <t>DMA-CL-004</t>
-  </si>
-  <si>
     <t>dma350_cmdlink_apb_noregclear_test</t>
   </si>
   <si>
@@ -828,9 +696,6 @@
     <t>Partial update loaded correctly; SRC/CTRL inherited from prior command; 3 copies to different destinations; completes.</t>
   </si>
   <si>
-    <t>DMA-CL-005</t>
-  </si>
-  <si>
     <t>dma350_cmdlink_apb_ctrl_only_test</t>
   </si>
   <si>
@@ -843,9 +708,6 @@
     <t>Minimal header decode correct; addresses/size inherited from APB command; completes.</t>
   </si>
   <si>
-    <t>DMA-CL-006</t>
-  </si>
-  <si>
     <t>dma350_cmdlink_apb_addr_size_test</t>
   </si>
   <si>
@@ -858,9 +720,6 @@
     <t>"Reload address + size" header loaded correctly; 3 copies to different regions; completes.</t>
   </si>
   <si>
-    <t>DMA-CL-007</t>
-  </si>
-  <si>
     <t>dma350_cmdlink_apb_transcfg_test</t>
   </si>
   <si>
@@ -873,9 +732,6 @@
     <t>Header TRANSCFG bits loaded correctly; AXI burst shape changes per config; completes.</t>
   </si>
   <si>
-    <t>DMA-CL-008</t>
-  </si>
-  <si>
     <t>dma350_cmdlink_apb_xaddrinc_test</t>
   </si>
   <si>
@@ -888,9 +744,6 @@
     <t>Header XADDRINC bit loaded correctly; address increments applied correctly per command; completes.</t>
   </si>
   <si>
-    <t>DMA-CL-009</t>
-  </si>
-  <si>
     <t>dma350_cmdlink_boot_single_test</t>
   </si>
   <si>
@@ -906,9 +759,6 @@
     <t>Responder must be ready BEFORE reset (boot fetch right after reset).</t>
   </si>
   <si>
-    <t>DMA-CL-010</t>
-  </si>
-  <si>
     <t>dma350_cmdlink_boot_chain_test</t>
   </si>
   <si>
@@ -922,9 +772,6 @@
   </si>
   <si>
     <t>Responder must be ready before reset.</t>
-  </si>
-  <si>
-    <t>DMA-CL-011</t>
   </si>
   <si>
     <t>dma350_cmdlink_apb_example_test</t>
@@ -1545,30 +1392,51 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="412" row="2">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{CFCCB2A3-0535-4376-951F-201451B3005C}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;9f8f3209-7f5a-4bcf-b259-801dcbb2f580&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F705807-3751-4CC0-9EC5-D598C44B33ED}">
-  <dimension ref="A1:AQ53"/>
+  <dimension ref="A1:AP53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.77734375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="33" style="1" customWidth="1"/>
-    <col min="5" max="5" width="52.77734375" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" customWidth="1"/>
-    <col min="7" max="7" width="60.77734375" customWidth="1"/>
-    <col min="8" max="8" width="12.77734375" customWidth="1"/>
-    <col min="9" max="9" width="11.77734375" customWidth="1"/>
-    <col min="10" max="11" width="12.77734375" customWidth="1"/>
-    <col min="12" max="13" width="13.77734375" customWidth="1"/>
-    <col min="14" max="14" width="18.77734375" customWidth="1"/>
-    <col min="17" max="17" width="29" customWidth="1"/>
-    <col min="41" max="41" width="30.77734375" customWidth="1"/>
-    <col min="42" max="42" width="12.77734375" customWidth="1"/>
-    <col min="43" max="43" width="40.77734375" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="33" style="1" customWidth="1"/>
+    <col min="4" max="4" width="52.77734375" customWidth="1"/>
+    <col min="5" max="5" width="40.77734375" customWidth="1"/>
+    <col min="6" max="6" width="60.77734375" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" customWidth="1"/>
+    <col min="8" max="8" width="11.77734375" customWidth="1"/>
+    <col min="9" max="10" width="12.77734375" customWidth="1"/>
+    <col min="11" max="12" width="13.77734375" customWidth="1"/>
+    <col min="13" max="13" width="18.77734375" customWidth="1"/>
+    <col min="16" max="16" width="29" customWidth="1"/>
+    <col min="40" max="40" width="30.77734375" customWidth="1"/>
+    <col min="41" max="41" width="12.77734375" customWidth="1"/>
+    <col min="42" max="42" width="40.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:42" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1613,9 +1481,8 @@
       <c r="AN1" s="21"/>
       <c r="AO1" s="21"/>
       <c r="AP1" s="21"/>
-      <c r="AQ1" s="21"/>
-    </row>
-    <row r="2" spans="1:43" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:42" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1660,9 +1527,8 @@
       <c r="AN2" s="23"/>
       <c r="AO2" s="23"/>
       <c r="AP2" s="23"/>
-      <c r="AQ2" s="23"/>
-    </row>
-    <row r="3" spans="1:43" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:42" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -1711,9 +1577,7 @@
       <c r="P3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="4" t="s">
-        <v>18</v>
-      </c>
+      <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
       <c r="T3" s="4"/>
@@ -1739,56 +1603,53 @@
       <c r="AN3" s="4"/>
       <c r="AO3" s="4"/>
       <c r="AP3" s="4"/>
-      <c r="AQ3" s="4"/>
-    </row>
-    <row r="4" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="I4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="K4" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L4" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="L4" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M4" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6" t="s">
-        <v>30</v>
-      </c>
+      <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
       <c r="S4" s="6"/>
       <c r="T4" s="6"/>
@@ -1814,51 +1675,48 @@
       <c r="AN4" s="6"/>
       <c r="AO4" s="6"/>
       <c r="AP4" s="6"/>
-      <c r="AQ4" s="6"/>
-    </row>
-    <row r="5" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>2</v>
       </c>
       <c r="B5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="F5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="G5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="11" t="s">
+      <c r="H5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="K5" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L5" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M5" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N5" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N5" s="9"/>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
@@ -1887,51 +1745,48 @@
       <c r="AN5" s="9"/>
       <c r="AO5" s="9"/>
       <c r="AP5" s="9"/>
-      <c r="AQ5" s="9"/>
-    </row>
-    <row r="6" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="G6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="J6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="K6" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L6" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M6" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N6" s="6"/>
       <c r="O6" s="6"/>
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
@@ -1960,56 +1815,53 @@
       <c r="AN6" s="6"/>
       <c r="AO6" s="6"/>
       <c r="AP6" s="6"/>
-      <c r="AQ6" s="6"/>
-    </row>
-    <row r="7" spans="1:43" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>4</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="I7" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L7" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M7" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9" t="s">
-        <v>48</v>
-      </c>
+      <c r="Q7" s="9"/>
       <c r="R7" s="9"/>
       <c r="S7" s="9"/>
       <c r="T7" s="9"/>
@@ -2035,56 +1887,53 @@
       <c r="AN7" s="9"/>
       <c r="AO7" s="9"/>
       <c r="AP7" s="9"/>
-      <c r="AQ7" s="9"/>
-    </row>
-    <row r="8" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
         <v>5</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="G8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L8" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L8" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M8" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N8" s="6"/>
       <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6" t="s">
-        <v>54</v>
-      </c>
+      <c r="P8" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
       <c r="S8" s="6"/>
       <c r="T8" s="6"/>
@@ -2110,56 +1959,53 @@
       <c r="AN8" s="6"/>
       <c r="AO8" s="6"/>
       <c r="AP8" s="6"/>
-      <c r="AQ8" s="6"/>
-    </row>
-    <row r="9" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>6</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>56</v>
+        <v>49</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>50</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="G9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L9" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L9" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M9" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N9" s="9"/>
       <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="9" t="s">
-        <v>54</v>
-      </c>
+      <c r="P9" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q9" s="9"/>
       <c r="R9" s="9"/>
       <c r="S9" s="9"/>
       <c r="T9" s="9"/>
@@ -2185,51 +2031,48 @@
       <c r="AN9" s="9"/>
       <c r="AO9" s="9"/>
       <c r="AP9" s="9"/>
-      <c r="AQ9" s="9"/>
-    </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>7</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>59</v>
+        <v>18</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>60</v>
+        <v>52</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J10" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L10" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L10" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M10" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N10" s="6"/>
       <c r="O10" s="6"/>
       <c r="P10" s="6"/>
       <c r="Q10" s="6"/>
@@ -2258,51 +2101,48 @@
       <c r="AN10" s="6"/>
       <c r="AO10" s="6"/>
       <c r="AP10" s="6"/>
-      <c r="AQ10" s="6"/>
-    </row>
-    <row r="11" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>8</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>66</v>
+        <v>57</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>58</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J11" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L11" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K11" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L11" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M11" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N11" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N11" s="9"/>
       <c r="O11" s="9"/>
       <c r="P11" s="9"/>
       <c r="Q11" s="9"/>
@@ -2331,56 +2171,53 @@
       <c r="AN11" s="9"/>
       <c r="AO11" s="9"/>
       <c r="AP11" s="9"/>
-      <c r="AQ11" s="9"/>
-    </row>
-    <row r="12" spans="1:43" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>71</v>
+        <v>61</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I12" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="G12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L12" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L12" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M12" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N12" s="6"/>
       <c r="O12" s="6"/>
-      <c r="P12" s="6"/>
-      <c r="Q12" s="6" t="s">
-        <v>75</v>
-      </c>
+      <c r="P12" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q12" s="6"/>
       <c r="R12" s="6"/>
       <c r="S12" s="6"/>
       <c r="T12" s="6"/>
@@ -2406,51 +2243,48 @@
       <c r="AN12" s="6"/>
       <c r="AO12" s="6"/>
       <c r="AP12" s="6"/>
-      <c r="AQ12" s="6"/>
-    </row>
-    <row r="13" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
         <v>10</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>77</v>
+        <v>66</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>67</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J13" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L13" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M13" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K13" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L13" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M13" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N13" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N13" s="9"/>
       <c r="O13" s="9"/>
       <c r="P13" s="9"/>
       <c r="Q13" s="9"/>
@@ -2479,51 +2313,48 @@
       <c r="AN13" s="9"/>
       <c r="AO13" s="9"/>
       <c r="AP13" s="9"/>
-      <c r="AQ13" s="9"/>
-    </row>
-    <row r="14" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>11</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>82</v>
+        <v>70</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I14" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J14" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L14" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M14" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K14" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L14" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M14" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
       <c r="Q14" s="6"/>
@@ -2552,51 +2383,48 @@
       <c r="AN14" s="6"/>
       <c r="AO14" s="6"/>
       <c r="AP14" s="6"/>
-      <c r="AQ14" s="6"/>
-    </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>12</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>87</v>
+        <v>74</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I15" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J15" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L15" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M15" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K15" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L15" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M15" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N15" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N15" s="9"/>
       <c r="O15" s="9"/>
       <c r="P15" s="9"/>
       <c r="Q15" s="9"/>
@@ -2625,56 +2453,53 @@
       <c r="AN15" s="9"/>
       <c r="AO15" s="9"/>
       <c r="AP15" s="9"/>
-      <c r="AQ15" s="9"/>
-    </row>
-    <row r="16" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>13</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>91</v>
+        <v>77</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="K16" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L16" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M16" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K16" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L16" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M16" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N16" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N16" s="6"/>
       <c r="O16" s="6"/>
-      <c r="P16" s="6"/>
-      <c r="Q16" s="6" t="s">
-        <v>95</v>
-      </c>
+      <c r="P16" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
       <c r="S16" s="6"/>
       <c r="T16" s="6"/>
@@ -2700,51 +2525,48 @@
       <c r="AN16" s="6"/>
       <c r="AO16" s="6"/>
       <c r="AP16" s="6"/>
-      <c r="AQ16" s="6"/>
-    </row>
-    <row r="17" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>14</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>97</v>
+        <v>82</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>83</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J17" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L17" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M17" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K17" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L17" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M17" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N17" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N17" s="9"/>
       <c r="O17" s="9"/>
       <c r="P17" s="9"/>
       <c r="Q17" s="9"/>
@@ -2773,51 +2595,48 @@
       <c r="AN17" s="9"/>
       <c r="AO17" s="9"/>
       <c r="AP17" s="9"/>
-      <c r="AQ17" s="9"/>
-    </row>
-    <row r="18" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>15</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>102</v>
+        <v>86</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I18" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J18" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L18" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M18" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L18" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M18" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N18" s="6"/>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
       <c r="Q18" s="6"/>
@@ -2846,51 +2665,48 @@
       <c r="AN18" s="6"/>
       <c r="AO18" s="6"/>
       <c r="AP18" s="6"/>
-      <c r="AQ18" s="6"/>
-    </row>
-    <row r="19" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>16</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>105</v>
+        <v>18</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>106</v>
+        <v>89</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>90</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J19" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L19" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M19" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K19" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L19" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M19" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N19" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N19" s="9"/>
       <c r="O19" s="9"/>
       <c r="P19" s="9"/>
       <c r="Q19" s="9"/>
@@ -2919,51 +2735,48 @@
       <c r="AN19" s="9"/>
       <c r="AO19" s="9"/>
       <c r="AP19" s="9"/>
-      <c r="AQ19" s="9"/>
-    </row>
-    <row r="20" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>17</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>111</v>
+        <v>93</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I20" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J20" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L20" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M20" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K20" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L20" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M20" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N20" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N20" s="6"/>
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
       <c r="Q20" s="6"/>
@@ -2992,51 +2805,48 @@
       <c r="AN20" s="6"/>
       <c r="AO20" s="6"/>
       <c r="AP20" s="6"/>
-      <c r="AQ20" s="6"/>
-    </row>
-    <row r="21" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>18</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>116</v>
+        <v>97</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>98</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I21" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J21" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L21" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M21" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K21" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L21" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M21" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N21" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N21" s="9"/>
       <c r="O21" s="9"/>
       <c r="P21" s="9"/>
       <c r="Q21" s="9"/>
@@ -3065,51 +2875,48 @@
       <c r="AN21" s="9"/>
       <c r="AO21" s="9"/>
       <c r="AP21" s="9"/>
-      <c r="AQ21" s="9"/>
-    </row>
-    <row r="22" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>19</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>120</v>
+        <v>100</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I22" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J22" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L22" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M22" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K22" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L22" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M22" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N22" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N22" s="6"/>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="6"/>
@@ -3138,56 +2945,53 @@
       <c r="AN22" s="6"/>
       <c r="AO22" s="6"/>
       <c r="AP22" s="6"/>
-      <c r="AQ22" s="6"/>
-    </row>
-    <row r="23" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>20</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>125</v>
+        <v>104</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>105</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J23" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L23" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M23" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K23" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L23" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M23" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N23" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N23" s="9"/>
       <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="9" t="s">
-        <v>129</v>
-      </c>
+      <c r="P23" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="S23" s="9"/>
       <c r="T23" s="9"/>
@@ -3213,56 +3017,53 @@
       <c r="AN23" s="9"/>
       <c r="AO23" s="9"/>
       <c r="AP23" s="9"/>
-      <c r="AQ23" s="9"/>
-    </row>
-    <row r="24" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5">
         <v>21</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>131</v>
+        <v>109</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J24" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L24" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M24" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K24" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L24" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M24" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N24" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N24" s="6"/>
       <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6" t="s">
-        <v>135</v>
-      </c>
+      <c r="P24" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q24" s="6"/>
       <c r="R24" s="6"/>
       <c r="S24" s="6"/>
       <c r="T24" s="6"/>
@@ -3288,51 +3089,48 @@
       <c r="AN24" s="6"/>
       <c r="AO24" s="6"/>
       <c r="AP24" s="6"/>
-      <c r="AQ24" s="6"/>
-    </row>
-    <row r="25" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>22</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>137</v>
+        <v>114</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>115</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>140</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J25" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L25" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M25" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K25" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L25" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M25" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N25" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N25" s="9"/>
       <c r="O25" s="9"/>
       <c r="P25" s="9"/>
       <c r="Q25" s="9"/>
@@ -3361,51 +3159,48 @@
       <c r="AN25" s="9"/>
       <c r="AO25" s="9"/>
       <c r="AP25" s="9"/>
-      <c r="AQ25" s="9"/>
-    </row>
-    <row r="26" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>23</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>141</v>
+        <v>18</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>142</v>
+        <v>118</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I26" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J26" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K26" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L26" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M26" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K26" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L26" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M26" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N26" s="6"/>
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
       <c r="Q26" s="6"/>
@@ -3434,51 +3229,48 @@
       <c r="AN26" s="6"/>
       <c r="AO26" s="6"/>
       <c r="AP26" s="6"/>
-      <c r="AQ26" s="6"/>
-    </row>
-    <row r="27" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
         <v>24</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>146</v>
+        <v>18</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>147</v>
+        <v>122</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>123</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I27" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J27" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K27" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L27" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M27" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K27" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L27" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M27" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N27" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N27" s="9"/>
       <c r="O27" s="9"/>
       <c r="P27" s="9"/>
       <c r="Q27" s="9"/>
@@ -3507,51 +3299,48 @@
       <c r="AN27" s="9"/>
       <c r="AO27" s="9"/>
       <c r="AP27" s="9"/>
-      <c r="AQ27" s="9"/>
-    </row>
-    <row r="28" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>25</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>153</v>
+        <v>127</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>128</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I28" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J28" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J28" s="12" t="s">
+      <c r="K28" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L28" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M28" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K28" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L28" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M28" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N28" s="6"/>
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
       <c r="Q28" s="6"/>
@@ -3580,56 +3369,53 @@
       <c r="AN28" s="6"/>
       <c r="AO28" s="6"/>
       <c r="AP28" s="6"/>
-      <c r="AQ28" s="6"/>
-    </row>
-    <row r="29" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>26</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>159</v>
+        <v>132</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="I29" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J29" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K29" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L29" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M29" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K29" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L29" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M29" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N29" s="9"/>
       <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9" t="s">
-        <v>163</v>
-      </c>
+      <c r="P29" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
       <c r="S29" s="9"/>
       <c r="T29" s="9"/>
@@ -3655,51 +3441,48 @@
       <c r="AN29" s="9"/>
       <c r="AO29" s="9"/>
       <c r="AP29" s="9"/>
-      <c r="AQ29" s="9"/>
-    </row>
-    <row r="30" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>27</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>164</v>
+        <v>126</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>165</v>
+        <v>137</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>138</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I30" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J30" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K30" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L30" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M30" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K30" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L30" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M30" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N30" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N30" s="6"/>
       <c r="O30" s="6"/>
       <c r="P30" s="6"/>
       <c r="Q30" s="6"/>
@@ -3728,51 +3511,48 @@
       <c r="AN30" s="6"/>
       <c r="AO30" s="6"/>
       <c r="AP30" s="6"/>
-      <c r="AQ30" s="6"/>
-    </row>
-    <row r="31" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
         <v>28</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>170</v>
+        <v>141</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>142</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="I31" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J31" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K31" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L31" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M31" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K31" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L31" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M31" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N31" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N31" s="9"/>
       <c r="O31" s="9"/>
       <c r="P31" s="9"/>
       <c r="Q31" s="9"/>
@@ -3801,51 +3581,48 @@
       <c r="AN31" s="9"/>
       <c r="AO31" s="9"/>
       <c r="AP31" s="9"/>
-      <c r="AQ31" s="9"/>
-    </row>
-    <row r="32" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>29</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>174</v>
+        <v>126</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>175</v>
+        <v>145</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I32" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J32" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J32" s="12" t="s">
+      <c r="K32" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L32" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M32" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K32" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L32" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M32" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N32" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N32" s="6"/>
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
       <c r="Q32" s="6"/>
@@ -3874,56 +3651,53 @@
       <c r="AN32" s="6"/>
       <c r="AO32" s="6"/>
       <c r="AP32" s="6"/>
-      <c r="AQ32" s="6"/>
-    </row>
-    <row r="33" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
         <v>30</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>179</v>
+        <v>126</v>
       </c>
       <c r="C33" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E33" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F33" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="D33" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="I33" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J33" s="12" t="s">
+      <c r="G33" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K33" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L33" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M33" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K33" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L33" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M33" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N33" s="9"/>
       <c r="O33" s="9"/>
-      <c r="P33" s="9"/>
-      <c r="Q33" s="9" t="s">
-        <v>184</v>
-      </c>
+      <c r="P33" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="9"/>
       <c r="T33" s="9"/>
@@ -3949,51 +3723,48 @@
       <c r="AN33" s="9"/>
       <c r="AO33" s="9"/>
       <c r="AP33" s="9"/>
-      <c r="AQ33" s="9"/>
-    </row>
-    <row r="34" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>31</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>185</v>
+        <v>126</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>186</v>
+        <v>154</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="H34" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="I34" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J34" s="12" t="s">
+      <c r="G34" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L34" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M34" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K34" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L34" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M34" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N34" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N34" s="6"/>
       <c r="O34" s="6"/>
       <c r="P34" s="6"/>
       <c r="Q34" s="6"/>
@@ -4022,51 +3793,48 @@
       <c r="AN34" s="6"/>
       <c r="AO34" s="6"/>
       <c r="AP34" s="6"/>
-      <c r="AQ34" s="6"/>
-    </row>
-    <row r="35" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
         <v>32</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>190</v>
+        <v>126</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>191</v>
+        <v>158</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>159</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="I35" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J35" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K35" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L35" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M35" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K35" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L35" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M35" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N35" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N35" s="9"/>
       <c r="O35" s="9"/>
       <c r="P35" s="9"/>
       <c r="Q35" s="9"/>
@@ -4095,56 +3863,53 @@
       <c r="AN35" s="9"/>
       <c r="AO35" s="9"/>
       <c r="AP35" s="9"/>
-      <c r="AQ35" s="9"/>
-    </row>
-    <row r="36" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>33</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>195</v>
+        <v>126</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>196</v>
+        <v>162</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="I36" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="H36" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J36" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J36" s="12" t="s">
+      <c r="K36" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L36" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M36" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K36" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L36" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M36" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N36" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N36" s="6"/>
       <c r="O36" s="6"/>
-      <c r="P36" s="6"/>
-      <c r="Q36" s="6" t="s">
-        <v>201</v>
-      </c>
+      <c r="P36" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
       <c r="S36" s="6"/>
       <c r="T36" s="6"/>
@@ -4170,56 +3935,53 @@
       <c r="AN36" s="6"/>
       <c r="AO36" s="6"/>
       <c r="AP36" s="6"/>
-      <c r="AQ36" s="6"/>
-    </row>
-    <row r="37" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
         <v>34</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>202</v>
+        <v>126</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>203</v>
+        <v>168</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>169</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>204</v>
+        <v>170</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="I37" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J37" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="G37" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K37" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L37" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M37" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K37" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L37" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M37" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N37" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N37" s="9"/>
       <c r="O37" s="9"/>
-      <c r="P37" s="9"/>
-      <c r="Q37" s="9" t="s">
-        <v>207</v>
-      </c>
+      <c r="P37" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
       <c r="T37" s="9"/>
@@ -4245,51 +4007,48 @@
       <c r="AN37" s="9"/>
       <c r="AO37" s="9"/>
       <c r="AP37" s="9"/>
-      <c r="AQ37" s="9"/>
-    </row>
-    <row r="38" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>35</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>208</v>
+        <v>126</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>209</v>
+        <v>173</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>211</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="I38" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J38" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K38" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L38" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M38" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K38" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L38" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M38" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N38" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N38" s="6"/>
       <c r="O38" s="6"/>
       <c r="P38" s="6"/>
       <c r="Q38" s="6"/>
@@ -4318,56 +4077,53 @@
       <c r="AN38" s="6"/>
       <c r="AO38" s="6"/>
       <c r="AP38" s="6"/>
-      <c r="AQ38" s="6"/>
-    </row>
-    <row r="39" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
         <v>36</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>213</v>
+        <v>126</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>214</v>
+        <v>177</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>178</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>215</v>
+        <v>179</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="I39" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J39" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J39" s="12" t="s">
+      <c r="K39" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L39" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M39" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K39" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L39" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M39" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N39" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N39" s="9"/>
       <c r="O39" s="9"/>
-      <c r="P39" s="9"/>
-      <c r="Q39" s="9" t="s">
-        <v>219</v>
-      </c>
+      <c r="P39" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
       <c r="T39" s="9"/>
@@ -4393,51 +4149,48 @@
       <c r="AN39" s="9"/>
       <c r="AO39" s="9"/>
       <c r="AP39" s="9"/>
-      <c r="AQ39" s="9"/>
-    </row>
-    <row r="40" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>37</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>220</v>
+        <v>126</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>221</v>
+        <v>183</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>222</v>
+        <v>185</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="I40" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J40" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J40" s="12" t="s">
+      <c r="K40" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L40" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M40" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K40" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L40" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M40" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N40" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N40" s="6"/>
       <c r="O40" s="6"/>
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
@@ -4466,56 +4219,53 @@
       <c r="AN40" s="6"/>
       <c r="AO40" s="6"/>
       <c r="AP40" s="6"/>
-      <c r="AQ40" s="6"/>
-    </row>
-    <row r="41" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
         <v>38</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>226</v>
+        <v>126</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>227</v>
+        <v>188</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>189</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>228</v>
+        <v>190</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="I41" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J41" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="H41" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K41" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L41" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M41" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K41" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L41" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M41" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N41" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N41" s="9"/>
       <c r="O41" s="9"/>
-      <c r="P41" s="9"/>
-      <c r="Q41" s="9" t="s">
-        <v>231</v>
-      </c>
+      <c r="P41" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
       <c r="T41" s="9"/>
@@ -4541,56 +4291,53 @@
       <c r="AN41" s="9"/>
       <c r="AO41" s="9"/>
       <c r="AP41" s="9"/>
-      <c r="AQ41" s="9"/>
-    </row>
-    <row r="42" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>39</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>232</v>
+        <v>126</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>233</v>
+        <v>193</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>194</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="H42" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="I42" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J42" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="H42" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K42" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L42" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M42" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K42" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L42" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M42" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N42" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N42" s="6"/>
       <c r="O42" s="6"/>
-      <c r="P42" s="6"/>
-      <c r="Q42" s="6" t="s">
-        <v>238</v>
-      </c>
+      <c r="P42" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
       <c r="S42" s="6"/>
       <c r="T42" s="6"/>
@@ -4616,51 +4363,48 @@
       <c r="AN42" s="6"/>
       <c r="AO42" s="6"/>
       <c r="AP42" s="6"/>
-      <c r="AQ42" s="6"/>
-    </row>
-    <row r="43" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8">
         <v>40</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>241</v>
+        <v>200</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>201</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="I43" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="G43" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H43" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J43" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J43" s="12" t="s">
+      <c r="K43" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L43" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M43" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K43" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L43" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M43" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N43" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N43" s="9"/>
       <c r="O43" s="9"/>
       <c r="P43" s="9"/>
       <c r="Q43" s="9"/>
@@ -4689,51 +4433,48 @@
       <c r="AN43" s="9"/>
       <c r="AO43" s="9"/>
       <c r="AP43" s="9"/>
-      <c r="AQ43" s="9"/>
-    </row>
-    <row r="44" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>41</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>246</v>
+        <v>199</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>247</v>
+        <v>205</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="H44" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="I44" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H44" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J44" s="12" t="s">
+      <c r="K44" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L44" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M44" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K44" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L44" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M44" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N44" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N44" s="6"/>
       <c r="O44" s="6"/>
       <c r="P44" s="6"/>
       <c r="Q44" s="6"/>
@@ -4762,51 +4503,48 @@
       <c r="AN44" s="6"/>
       <c r="AO44" s="6"/>
       <c r="AP44" s="6"/>
-      <c r="AQ44" s="6"/>
-    </row>
-    <row r="45" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8">
         <v>42</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>251</v>
+        <v>199</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>252</v>
+        <v>209</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>210</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="I45" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J45" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H45" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K45" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L45" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M45" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K45" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L45" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M45" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N45" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N45" s="9"/>
       <c r="O45" s="9"/>
       <c r="P45" s="9"/>
       <c r="Q45" s="9"/>
@@ -4835,51 +4573,48 @@
       <c r="AN45" s="9"/>
       <c r="AO45" s="9"/>
       <c r="AP45" s="9"/>
-      <c r="AQ45" s="9"/>
-    </row>
-    <row r="46" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>43</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>256</v>
+        <v>199</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>257</v>
+        <v>213</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>258</v>
+        <v>215</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="I46" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J46" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K46" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L46" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M46" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K46" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L46" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M46" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N46" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N46" s="6"/>
       <c r="O46" s="6"/>
       <c r="P46" s="6"/>
       <c r="Q46" s="6"/>
@@ -4908,51 +4643,48 @@
       <c r="AN46" s="6"/>
       <c r="AO46" s="6"/>
       <c r="AP46" s="6"/>
-      <c r="AQ46" s="6"/>
-    </row>
-    <row r="47" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="8">
         <v>44</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>261</v>
+        <v>199</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>262</v>
+        <v>217</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>218</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>263</v>
+        <v>219</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="G47" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="I47" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J47" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I47" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K47" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L47" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M47" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K47" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L47" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M47" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N47" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N47" s="9"/>
       <c r="O47" s="9"/>
       <c r="P47" s="9"/>
       <c r="Q47" s="9"/>
@@ -4981,51 +4713,48 @@
       <c r="AN47" s="9"/>
       <c r="AO47" s="9"/>
       <c r="AP47" s="9"/>
-      <c r="AQ47" s="9"/>
-    </row>
-    <row r="48" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>45</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>266</v>
+        <v>199</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>267</v>
+        <v>221</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>222</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>268</v>
+        <v>223</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="H48" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="I48" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J48" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K48" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L48" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M48" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K48" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L48" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M48" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N48" s="6"/>
       <c r="O48" s="6"/>
       <c r="P48" s="6"/>
       <c r="Q48" s="6"/>
@@ -5054,51 +4783,48 @@
       <c r="AN48" s="6"/>
       <c r="AO48" s="6"/>
       <c r="AP48" s="6"/>
-      <c r="AQ48" s="6"/>
-    </row>
-    <row r="49" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8">
         <v>46</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>271</v>
+        <v>199</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>272</v>
+        <v>225</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>226</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>273</v>
+        <v>227</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="I49" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J49" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I49" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K49" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L49" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M49" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K49" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L49" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M49" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N49" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N49" s="9"/>
       <c r="O49" s="9"/>
       <c r="P49" s="9"/>
       <c r="Q49" s="9"/>
@@ -5127,51 +4853,48 @@
       <c r="AN49" s="9"/>
       <c r="AO49" s="9"/>
       <c r="AP49" s="9"/>
-      <c r="AQ49" s="9"/>
-    </row>
-    <row r="50" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>47</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>276</v>
+        <v>199</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>277</v>
+        <v>229</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>230</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>278</v>
+        <v>231</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="H50" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="I50" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="J50" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K50" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L50" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M50" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K50" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L50" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M50" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N50" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N50" s="6"/>
       <c r="O50" s="6"/>
       <c r="P50" s="6"/>
       <c r="Q50" s="6"/>
@@ -5200,56 +4923,53 @@
       <c r="AN50" s="6"/>
       <c r="AO50" s="6"/>
       <c r="AP50" s="6"/>
-      <c r="AQ50" s="6"/>
-    </row>
-    <row r="51" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8">
         <v>48</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>281</v>
+        <v>199</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>282</v>
+        <v>233</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>234</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>283</v>
+        <v>235</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="H51" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="I51" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H51" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J51" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J51" s="12" t="s">
+      <c r="K51" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L51" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M51" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K51" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L51" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M51" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N51" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N51" s="9"/>
       <c r="O51" s="9"/>
-      <c r="P51" s="9"/>
-      <c r="Q51" s="9" t="s">
-        <v>286</v>
-      </c>
+      <c r="P51" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
       <c r="S51" s="9"/>
       <c r="T51" s="9"/>
@@ -5275,56 +4995,53 @@
       <c r="AN51" s="9"/>
       <c r="AO51" s="9"/>
       <c r="AP51" s="9"/>
-      <c r="AQ51" s="9"/>
-    </row>
-    <row r="52" spans="1:43" ht="41.4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <v>49</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>287</v>
+        <v>199</v>
       </c>
       <c r="C52" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E52" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="D52" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>289</v>
-      </c>
       <c r="F52" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="H52" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="I52" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H52" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I52" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J52" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="J52" s="12" t="s">
+      <c r="K52" s="7">
+        <v>46227</v>
+      </c>
+      <c r="L52" s="7">
+        <v>46227</v>
+      </c>
+      <c r="M52" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="K52" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L52" s="7">
-        <v>46227</v>
-      </c>
-      <c r="M52" s="7">
-        <v>46227</v>
-      </c>
-      <c r="N52" s="6" t="s">
-        <v>29</v>
-      </c>
+      <c r="N52" s="6"/>
       <c r="O52" s="6"/>
-      <c r="P52" s="6"/>
-      <c r="Q52" s="6" t="s">
-        <v>292</v>
-      </c>
+      <c r="P52" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
       <c r="S52" s="6"/>
       <c r="T52" s="6"/>
@@ -5350,56 +5067,53 @@
       <c r="AN52" s="6"/>
       <c r="AO52" s="6"/>
       <c r="AP52" s="6"/>
-      <c r="AQ52" s="6"/>
-    </row>
-    <row r="53" spans="1:43" ht="27.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:42" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="8">
         <v>50</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>293</v>
+        <v>199</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>294</v>
+        <v>243</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>244</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>295</v>
+        <v>245</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="H53" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="I53" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="G53" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I53" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J53" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J53" s="12" t="s">
+      <c r="K53" s="10">
+        <v>46227</v>
+      </c>
+      <c r="L53" s="10">
+        <v>46227</v>
+      </c>
+      <c r="M53" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="K53" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L53" s="10">
-        <v>46227</v>
-      </c>
-      <c r="M53" s="10">
-        <v>46227</v>
-      </c>
-      <c r="N53" s="9" t="s">
-        <v>29</v>
-      </c>
+      <c r="N53" s="9"/>
       <c r="O53" s="9"/>
-      <c r="P53" s="9"/>
-      <c r="Q53" s="9" t="s">
-        <v>298</v>
-      </c>
+      <c r="P53" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
       <c r="S53" s="9"/>
       <c r="T53" s="9"/>
@@ -5425,22 +5139,21 @@
       <c r="AN53" s="9"/>
       <c r="AO53" s="9"/>
       <c r="AP53" s="9"/>
-      <c r="AQ53" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AQ53" xr:uid="{3F705807-3751-4CC0-9EC5-D598C44B33ED}"/>
+  <autoFilter ref="A3:AP53" xr:uid="{3F705807-3751-4CC0-9EC5-D598C44B33ED}"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:AQ1"/>
-    <mergeCell ref="A2:AQ2"/>
+    <mergeCell ref="A1:AP1"/>
+    <mergeCell ref="A2:AP2"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J53" xr:uid="{DE2944AD-92D0-408D-9B63-6D8A7D894832}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I53" xr:uid="{DE2944AD-92D0-408D-9B63-6D8A7D894832}">
       <formula1>"Not Run,Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4:K53" xr:uid="{7EAE88AE-FE00-4F18-A71D-C92487A40AB5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J4:J53" xr:uid="{7EAE88AE-FE00-4F18-A71D-C92487A40AB5}">
       <formula1>"Not Coded,Coded,In Review,Reviewed,Closed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I4:I53" xr:uid="{D12213F3-0CFE-49BB-999D-BCE66099CEF2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H53" xr:uid="{D12213F3-0CFE-49BB-999D-BCE66099CEF2}">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5460,25 +5173,25 @@
   <sheetData>
     <row r="1" spans="1:3" ht="25.95" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="24" t="s">
-        <v>299</v>
+        <v>248</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>300</v>
+        <v>249</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>301</v>
+        <v>250</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" s="16">
         <v>24</v>
@@ -5489,7 +5202,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="16" t="s">
-        <v>240</v>
+        <v>199</v>
       </c>
       <c r="B5" s="16">
         <v>11</v>
@@ -5500,7 +5213,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="16" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="B6" s="16">
         <v>15</v>
@@ -5511,7 +5224,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
-        <v>302</v>
+        <v>251</v>
       </c>
       <c r="B7" s="18">
         <v>50</v>
@@ -5522,21 +5235,21 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>303</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>304</v>
+        <v>253</v>
       </c>
       <c r="C10" s="3"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B11" s="16">
         <v>50</v>

--- a/DMA350_Testlist_Report.xlsx
+++ b/DMA350_Testlist_Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/83377f57b735e897/Máy tính/DMA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{2625DCD3-86CB-454F-AA68-A012DEAA1CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82F9067E-796E-4843-9AE8-260C5C380D06}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="8_{2625DCD3-86CB-454F-AA68-A012DEAA1CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C3BCD34-1D83-4200-8C77-FA8B8860EDED}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A5EF85DA-40B8-41A9-8419-62FC068EFE4F}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="256">
   <si>
     <t>DMA-350 DMAC - TEST LIST REPORT (UVM Verification)</t>
   </si>
@@ -805,6 +805,12 @@
   </si>
   <si>
     <t>Count</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>31/6/2026</t>
   </si>
 </sst>
 </file>
@@ -1630,16 +1636,16 @@
         <v>24</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>25</v>
+        <v>254</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>26</v>
       </c>
       <c r="K4" s="7">
-        <v>46227</v>
-      </c>
-      <c r="L4" s="7">
-        <v>46227</v>
+        <v>46209</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>255</v>
       </c>
       <c r="M4" s="6" t="s">
         <v>27</v>
@@ -1702,7 +1708,7 @@
         <v>24</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>25</v>
+        <v>254</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>26</v>
@@ -1772,7 +1778,7 @@
         <v>24</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>25</v>
+        <v>254</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>26</v>
@@ -1842,7 +1848,7 @@
         <v>42</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>25</v>
+        <v>254</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>26</v>
